--- a/02-Execucao/03-Execucao_Procedimentos/02-Resultados_Auditoria/tabelas_consolidadas_auditoria.xlsx
+++ b/02-Execucao/03-Execucao_Procedimentos/02-Resultados_Auditoria/tabelas_consolidadas_auditoria.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6580" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6256" uniqueCount="313">
   <si>
     <t>Nome</t>
   </si>
@@ -6497,13 +6497,7 @@
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
-        <v>258</v>
-      </c>
       <c r="D2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E2" t="s">
         <v>258</v>
       </c>
       <c r="G2" t="s">
@@ -6612,13 +6606,7 @@
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
-        <v>258</v>
-      </c>
       <c r="D4" t="s">
-        <v>258</v>
-      </c>
-      <c r="E4" t="s">
         <v>258</v>
       </c>
       <c r="G4" t="s">
@@ -6683,16 +6671,10 @@
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
-        <v>258</v>
-      </c>
       <c r="C5" t="s">
         <v>258</v>
       </c>
       <c r="D5" t="s">
-        <v>258</v>
-      </c>
-      <c r="E5" t="s">
         <v>258</v>
       </c>
       <c r="G5" t="s">
@@ -6760,9 +6742,6 @@
       <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
-        <v>258</v>
-      </c>
       <c r="C6" t="s">
         <v>258</v>
       </c>
@@ -6770,9 +6749,6 @@
         <v>258</v>
       </c>
       <c r="E6" t="s">
-        <v>258</v>
-      </c>
-      <c r="F6" t="s">
         <v>258</v>
       </c>
       <c r="G6" t="s">
@@ -6905,16 +6881,10 @@
       <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" t="s">
-        <v>258</v>
-      </c>
       <c r="E8" t="s">
         <v>258</v>
       </c>
       <c r="F8" t="s">
-        <v>258</v>
-      </c>
-      <c r="G8" t="s">
         <v>258</v>
       </c>
       <c r="H8" t="s">
@@ -6976,9 +6946,6 @@
       <c r="A9" t="s">
         <v>15</v>
       </c>
-      <c r="B9" t="s">
-        <v>258</v>
-      </c>
       <c r="E9" t="s">
         <v>258</v>
       </c>
@@ -7047,13 +7014,7 @@
       <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="B10" t="s">
-        <v>258</v>
-      </c>
       <c r="D10" t="s">
-        <v>258</v>
-      </c>
-      <c r="E10" t="s">
         <v>258</v>
       </c>
       <c r="G10" t="s">
@@ -7153,9 +7114,6 @@
       <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="B12" t="s">
-        <v>258</v>
-      </c>
       <c r="C12" t="s">
         <v>258</v>
       </c>
@@ -7218,9 +7176,6 @@
       <c r="A13" t="s">
         <v>19</v>
       </c>
-      <c r="B13" t="s">
-        <v>258</v>
-      </c>
       <c r="D13" t="s">
         <v>258</v>
       </c>
@@ -7333,13 +7288,7 @@
       <c r="A15" t="s">
         <v>21</v>
       </c>
-      <c r="B15" t="s">
-        <v>258</v>
-      </c>
       <c r="D15" t="s">
-        <v>258</v>
-      </c>
-      <c r="E15" t="s">
         <v>258</v>
       </c>
       <c r="G15" t="s">
@@ -7410,9 +7359,6 @@
       <c r="C16" t="s">
         <v>258</v>
       </c>
-      <c r="F16" t="s">
-        <v>258</v>
-      </c>
       <c r="H16" t="s">
         <v>258</v>
       </c>
@@ -7472,16 +7418,10 @@
       <c r="A17" t="s">
         <v>23</v>
       </c>
-      <c r="B17" t="s">
-        <v>258</v>
-      </c>
       <c r="C17" t="s">
         <v>258</v>
       </c>
       <c r="D17" t="s">
-        <v>258</v>
-      </c>
-      <c r="E17" t="s">
         <v>258</v>
       </c>
       <c r="G17" t="s">
@@ -7608,9 +7548,6 @@
       <c r="A19" t="s">
         <v>25</v>
       </c>
-      <c r="B19" t="s">
-        <v>258</v>
-      </c>
       <c r="C19" t="s">
         <v>258</v>
       </c>
@@ -7618,9 +7555,6 @@
         <v>258</v>
       </c>
       <c r="E19" t="s">
-        <v>258</v>
-      </c>
-      <c r="G19" t="s">
         <v>258</v>
       </c>
       <c r="H19" t="s">
@@ -7664,9 +7598,6 @@
       <c r="A20" t="s">
         <v>26</v>
       </c>
-      <c r="B20" t="s">
-        <v>258</v>
-      </c>
       <c r="C20" t="s">
         <v>258</v>
       </c>
@@ -7729,9 +7660,6 @@
       <c r="A21" t="s">
         <v>28</v>
       </c>
-      <c r="B21" t="s">
-        <v>258</v>
-      </c>
       <c r="C21" t="s">
         <v>258</v>
       </c>
@@ -7806,16 +7734,10 @@
       <c r="A22" t="s">
         <v>29</v>
       </c>
-      <c r="B22" t="s">
-        <v>258</v>
-      </c>
       <c r="C22" t="s">
         <v>258</v>
       </c>
       <c r="D22" t="s">
-        <v>258</v>
-      </c>
-      <c r="E22" t="s">
         <v>258</v>
       </c>
       <c r="G22" t="s">
@@ -7877,16 +7799,7 @@
       <c r="A23" t="s">
         <v>30</v>
       </c>
-      <c r="B23" t="s">
-        <v>258</v>
-      </c>
       <c r="D23" t="s">
-        <v>258</v>
-      </c>
-      <c r="E23" t="s">
-        <v>258</v>
-      </c>
-      <c r="G23" t="s">
         <v>258</v>
       </c>
       <c r="H23" t="s">
@@ -7954,9 +7867,6 @@
       <c r="A24" t="s">
         <v>31</v>
       </c>
-      <c r="B24" t="s">
-        <v>258</v>
-      </c>
       <c r="C24" t="s">
         <v>258</v>
       </c>
@@ -8022,16 +7932,10 @@
       <c r="A25" t="s">
         <v>32</v>
       </c>
-      <c r="B25" t="s">
-        <v>258</v>
-      </c>
       <c r="C25" t="s">
         <v>258</v>
       </c>
       <c r="D25" t="s">
-        <v>258</v>
-      </c>
-      <c r="E25" t="s">
         <v>258</v>
       </c>
       <c r="G25" t="s">
@@ -8099,12 +8003,6 @@
       <c r="A26" t="s">
         <v>33</v>
       </c>
-      <c r="B26" t="s">
-        <v>258</v>
-      </c>
-      <c r="E26" t="s">
-        <v>258</v>
-      </c>
       <c r="G26" t="s">
         <v>258</v>
       </c>
@@ -8179,9 +8077,6 @@
       <c r="F27" t="s">
         <v>258</v>
       </c>
-      <c r="G27" t="s">
-        <v>258</v>
-      </c>
       <c r="H27" t="s">
         <v>258</v>
       </c>
@@ -8226,9 +8121,6 @@
       <c r="A28" t="s">
         <v>35</v>
       </c>
-      <c r="B28" t="s">
-        <v>258</v>
-      </c>
       <c r="C28" t="s">
         <v>258</v>
       </c>
@@ -8297,19 +8189,10 @@
       <c r="A29" t="s">
         <v>36</v>
       </c>
-      <c r="B29" t="s">
-        <v>258</v>
-      </c>
       <c r="C29" t="s">
         <v>258</v>
       </c>
       <c r="D29" t="s">
-        <v>258</v>
-      </c>
-      <c r="E29" t="s">
-        <v>258</v>
-      </c>
-      <c r="G29" t="s">
         <v>258</v>
       </c>
       <c r="H29" t="s">
@@ -8377,9 +8260,6 @@
       <c r="A30" t="s">
         <v>37</v>
       </c>
-      <c r="B30" t="s">
-        <v>258</v>
-      </c>
       <c r="H30" t="s">
         <v>258</v>
       </c>
@@ -8439,13 +8319,7 @@
       <c r="A31" t="s">
         <v>38</v>
       </c>
-      <c r="B31" t="s">
-        <v>258</v>
-      </c>
       <c r="D31" t="s">
-        <v>258</v>
-      </c>
-      <c r="E31" t="s">
         <v>258</v>
       </c>
       <c r="G31" t="s">
@@ -8492,22 +8366,10 @@
       <c r="A32" t="s">
         <v>39</v>
       </c>
-      <c r="B32" t="s">
-        <v>258</v>
-      </c>
       <c r="C32" t="s">
         <v>258</v>
       </c>
       <c r="D32" t="s">
-        <v>258</v>
-      </c>
-      <c r="E32" t="s">
-        <v>258</v>
-      </c>
-      <c r="F32" t="s">
-        <v>258</v>
-      </c>
-      <c r="G32" t="s">
         <v>258</v>
       </c>
       <c r="H32" t="s">
@@ -8575,16 +8437,10 @@
       <c r="A33" t="s">
         <v>40</v>
       </c>
-      <c r="B33" t="s">
-        <v>258</v>
-      </c>
       <c r="C33" t="s">
         <v>258</v>
       </c>
       <c r="D33" t="s">
-        <v>258</v>
-      </c>
-      <c r="E33" t="s">
         <v>258</v>
       </c>
       <c r="G33" t="s">
@@ -8655,9 +8511,6 @@
       <c r="D34" t="s">
         <v>258</v>
       </c>
-      <c r="E34" t="s">
-        <v>258</v>
-      </c>
       <c r="F34" t="s">
         <v>258</v>
       </c>
@@ -8720,9 +8573,6 @@
       <c r="A35" t="s">
         <v>42</v>
       </c>
-      <c r="B35" t="s">
-        <v>258</v>
-      </c>
       <c r="D35" t="s">
         <v>258</v>
       </c>
@@ -8785,9 +8635,6 @@
       <c r="A36" t="s">
         <v>43</v>
       </c>
-      <c r="B36" t="s">
-        <v>258</v>
-      </c>
       <c r="H36" t="s">
         <v>258</v>
       </c>
@@ -8838,9 +8685,6 @@
       <c r="A37" t="s">
         <v>44</v>
       </c>
-      <c r="B37" t="s">
-        <v>258</v>
-      </c>
       <c r="C37" t="s">
         <v>258</v>
       </c>
@@ -8906,13 +8750,7 @@
       <c r="A38" t="s">
         <v>45</v>
       </c>
-      <c r="B38" t="s">
-        <v>258</v>
-      </c>
       <c r="D38" t="s">
-        <v>258</v>
-      </c>
-      <c r="E38" t="s">
         <v>258</v>
       </c>
       <c r="G38" t="s">
@@ -8971,9 +8809,6 @@
       <c r="A39" t="s">
         <v>46</v>
       </c>
-      <c r="B39" t="s">
-        <v>258</v>
-      </c>
       <c r="C39" t="s">
         <v>258</v>
       </c>
@@ -8981,9 +8816,6 @@
         <v>258</v>
       </c>
       <c r="E39" t="s">
-        <v>258</v>
-      </c>
-      <c r="G39" t="s">
         <v>258</v>
       </c>
       <c r="H39" t="s">
@@ -9045,16 +8877,10 @@
       <c r="A40" t="s">
         <v>47</v>
       </c>
-      <c r="B40" t="s">
-        <v>258</v>
-      </c>
       <c r="C40" t="s">
         <v>258</v>
       </c>
       <c r="D40" t="s">
-        <v>258</v>
-      </c>
-      <c r="E40" t="s">
         <v>258</v>
       </c>
       <c r="F40" t="s">
@@ -9157,9 +8983,6 @@
       <c r="A42" t="s">
         <v>49</v>
       </c>
-      <c r="B42" t="s">
-        <v>258</v>
-      </c>
       <c r="C42" t="s">
         <v>258</v>
       </c>
@@ -9260,9 +9083,6 @@
       <c r="A44" t="s">
         <v>52</v>
       </c>
-      <c r="B44" t="s">
-        <v>258</v>
-      </c>
       <c r="H44" t="s">
         <v>258</v>
       </c>
@@ -9292,9 +9112,6 @@
       <c r="A45" t="s">
         <v>53</v>
       </c>
-      <c r="B45" t="s">
-        <v>258</v>
-      </c>
       <c r="C45" t="s">
         <v>258</v>
       </c>
@@ -9366,12 +9183,6 @@
       <c r="A46" t="s">
         <v>54</v>
       </c>
-      <c r="B46" t="s">
-        <v>258</v>
-      </c>
-      <c r="F46" t="s">
-        <v>258</v>
-      </c>
       <c r="H46" t="s">
         <v>258</v>
       </c>
@@ -9404,9 +9215,6 @@
       <c r="A47" t="s">
         <v>55</v>
       </c>
-      <c r="B47" t="s">
-        <v>258</v>
-      </c>
       <c r="D47" t="s">
         <v>258</v>
       </c>
@@ -9463,9 +9271,6 @@
       <c r="A48" t="s">
         <v>56</v>
       </c>
-      <c r="B48" t="s">
-        <v>258</v>
-      </c>
       <c r="C48" t="s">
         <v>258</v>
       </c>
@@ -9543,9 +9348,6 @@
       <c r="D49" t="s">
         <v>258</v>
       </c>
-      <c r="F49" t="s">
-        <v>258</v>
-      </c>
       <c r="H49" t="s">
         <v>258</v>
       </c>
@@ -9593,9 +9395,6 @@
       <c r="A50" t="s">
         <v>58</v>
       </c>
-      <c r="B50" t="s">
-        <v>258</v>
-      </c>
       <c r="C50" t="s">
         <v>258</v>
       </c>
@@ -9603,9 +9402,6 @@
         <v>258</v>
       </c>
       <c r="E50" t="s">
-        <v>258</v>
-      </c>
-      <c r="G50" t="s">
         <v>258</v>
       </c>
       <c r="H50" t="s">
@@ -9670,16 +9466,10 @@
       <c r="A51" t="s">
         <v>59</v>
       </c>
-      <c r="B51" t="s">
-        <v>258</v>
-      </c>
       <c r="C51" t="s">
         <v>258</v>
       </c>
       <c r="D51" t="s">
-        <v>258</v>
-      </c>
-      <c r="E51" t="s">
         <v>258</v>
       </c>
       <c r="G51" t="s">
@@ -9741,13 +9531,7 @@
       <c r="A52" t="s">
         <v>60</v>
       </c>
-      <c r="B52" t="s">
-        <v>258</v>
-      </c>
       <c r="D52" t="s">
-        <v>258</v>
-      </c>
-      <c r="E52" t="s">
         <v>258</v>
       </c>
       <c r="G52" t="s">
@@ -9862,16 +9646,10 @@
       <c r="A54" t="s">
         <v>62</v>
       </c>
-      <c r="B54" t="s">
-        <v>258</v>
-      </c>
       <c r="C54" t="s">
         <v>258</v>
       </c>
       <c r="D54" t="s">
-        <v>258</v>
-      </c>
-      <c r="E54" t="s">
         <v>258</v>
       </c>
       <c r="G54" t="s">
@@ -9939,12 +9717,6 @@
       <c r="A55" t="s">
         <v>63</v>
       </c>
-      <c r="B55" t="s">
-        <v>258</v>
-      </c>
-      <c r="E55" t="s">
-        <v>258</v>
-      </c>
       <c r="G55" t="s">
         <v>258</v>
       </c>
@@ -9995,12 +9767,6 @@
       <c r="A56" t="s">
         <v>65</v>
       </c>
-      <c r="B56" t="s">
-        <v>258</v>
-      </c>
-      <c r="F56" t="s">
-        <v>258</v>
-      </c>
       <c r="H56" t="s">
         <v>258</v>
       </c>
@@ -10048,9 +9814,6 @@
       <c r="A57" t="s">
         <v>66</v>
       </c>
-      <c r="B57" t="s">
-        <v>258</v>
-      </c>
       <c r="D57" t="s">
         <v>258</v>
       </c>
@@ -10113,9 +9876,6 @@
       <c r="A58" t="s">
         <v>67</v>
       </c>
-      <c r="B58" t="s">
-        <v>258</v>
-      </c>
       <c r="C58" t="s">
         <v>258</v>
       </c>
@@ -10243,16 +10003,10 @@
       <c r="A60" t="s">
         <v>69</v>
       </c>
-      <c r="B60" t="s">
-        <v>258</v>
-      </c>
       <c r="C60" t="s">
         <v>258</v>
       </c>
       <c r="D60" t="s">
-        <v>258</v>
-      </c>
-      <c r="E60" t="s">
         <v>258</v>
       </c>
       <c r="G60" t="s">
@@ -10314,9 +10068,6 @@
       <c r="A61" t="s">
         <v>70</v>
       </c>
-      <c r="B61" t="s">
-        <v>258</v>
-      </c>
       <c r="C61" t="s">
         <v>258</v>
       </c>
@@ -10382,9 +10133,6 @@
       <c r="D62" t="s">
         <v>258</v>
       </c>
-      <c r="E62" t="s">
-        <v>258</v>
-      </c>
       <c r="F62" t="s">
         <v>258</v>
       </c>
@@ -10450,9 +10198,6 @@
       <c r="D63" t="s">
         <v>258</v>
       </c>
-      <c r="E63" t="s">
-        <v>258</v>
-      </c>
       <c r="G63" t="s">
         <v>258</v>
       </c>
@@ -10506,13 +10251,7 @@
       <c r="A64" t="s">
         <v>73</v>
       </c>
-      <c r="B64" t="s">
-        <v>258</v>
-      </c>
       <c r="D64" t="s">
-        <v>258</v>
-      </c>
-      <c r="E64" t="s">
         <v>258</v>
       </c>
       <c r="G64" t="s">
@@ -10577,9 +10316,6 @@
       <c r="A65" t="s">
         <v>74</v>
       </c>
-      <c r="B65" t="s">
-        <v>258</v>
-      </c>
       <c r="D65" t="s">
         <v>258</v>
       </c>
@@ -10645,16 +10381,10 @@
       <c r="A66" t="s">
         <v>75</v>
       </c>
-      <c r="B66" t="s">
-        <v>258</v>
-      </c>
       <c r="C66" t="s">
         <v>258</v>
       </c>
       <c r="D66" t="s">
-        <v>258</v>
-      </c>
-      <c r="E66" t="s">
         <v>258</v>
       </c>
       <c r="G66" t="s">
@@ -10716,9 +10446,6 @@
       <c r="A67" t="s">
         <v>76</v>
       </c>
-      <c r="E67" t="s">
-        <v>258</v>
-      </c>
       <c r="G67" t="s">
         <v>258</v>
       </c>
@@ -10748,13 +10475,7 @@
       <c r="A68" t="s">
         <v>77</v>
       </c>
-      <c r="B68" t="s">
-        <v>258</v>
-      </c>
       <c r="D68" t="s">
-        <v>258</v>
-      </c>
-      <c r="E68" t="s">
         <v>258</v>
       </c>
       <c r="G68" t="s">
@@ -10828,9 +10549,6 @@
       <c r="E69" t="s">
         <v>258</v>
       </c>
-      <c r="F69" t="s">
-        <v>258</v>
-      </c>
       <c r="G69" t="s">
         <v>258</v>
       </c>
@@ -10949,12 +10667,6 @@
       <c r="E71" t="s">
         <v>258</v>
       </c>
-      <c r="F71" t="s">
-        <v>258</v>
-      </c>
-      <c r="G71" t="s">
-        <v>258</v>
-      </c>
       <c r="H71" t="s">
         <v>258</v>
       </c>
@@ -10990,9 +10702,6 @@
       <c r="D72" t="s">
         <v>258</v>
       </c>
-      <c r="E72" t="s">
-        <v>258</v>
-      </c>
       <c r="G72" t="s">
         <v>258</v>
       </c>
@@ -11061,9 +10770,6 @@
       <c r="D73" t="s">
         <v>258</v>
       </c>
-      <c r="E73" t="s">
-        <v>258</v>
-      </c>
       <c r="G73" t="s">
         <v>258</v>
       </c>
@@ -11123,9 +10829,6 @@
       <c r="A74" t="s">
         <v>85</v>
       </c>
-      <c r="B74" t="s">
-        <v>258</v>
-      </c>
       <c r="C74" t="s">
         <v>258</v>
       </c>
@@ -11194,16 +10897,10 @@
       <c r="A75" t="s">
         <v>86</v>
       </c>
-      <c r="B75" t="s">
-        <v>258</v>
-      </c>
       <c r="C75" t="s">
         <v>258</v>
       </c>
       <c r="D75" t="s">
-        <v>258</v>
-      </c>
-      <c r="E75" t="s">
         <v>258</v>
       </c>
       <c r="G75" t="s">
@@ -11268,9 +10965,6 @@
       <c r="B76" t="s">
         <v>258</v>
       </c>
-      <c r="E76" t="s">
-        <v>258</v>
-      </c>
       <c r="G76" t="s">
         <v>258</v>
       </c>
@@ -11359,22 +11053,10 @@
       <c r="A78" t="s">
         <v>89</v>
       </c>
-      <c r="B78" t="s">
-        <v>258</v>
-      </c>
       <c r="C78" t="s">
         <v>258</v>
       </c>
       <c r="D78" t="s">
-        <v>258</v>
-      </c>
-      <c r="E78" t="s">
-        <v>258</v>
-      </c>
-      <c r="F78" t="s">
-        <v>258</v>
-      </c>
-      <c r="G78" t="s">
         <v>258</v>
       </c>
       <c r="H78" t="s">
@@ -11442,9 +11124,6 @@
       <c r="A79" t="s">
         <v>90</v>
       </c>
-      <c r="B79" t="s">
-        <v>258</v>
-      </c>
       <c r="D79" t="s">
         <v>258</v>
       </c>
@@ -11510,9 +11189,6 @@
       <c r="A80" t="s">
         <v>91</v>
       </c>
-      <c r="B80" t="s">
-        <v>258</v>
-      </c>
       <c r="D80" t="s">
         <v>258</v>
       </c>
@@ -11575,12 +11251,6 @@
       <c r="A81" t="s">
         <v>92</v>
       </c>
-      <c r="B81" t="s">
-        <v>258</v>
-      </c>
-      <c r="E81" t="s">
-        <v>258</v>
-      </c>
       <c r="G81" t="s">
         <v>258</v>
       </c>
@@ -11646,16 +11316,7 @@
       <c r="A82" t="s">
         <v>93</v>
       </c>
-      <c r="B82" t="s">
-        <v>258</v>
-      </c>
       <c r="D82" t="s">
-        <v>258</v>
-      </c>
-      <c r="E82" t="s">
-        <v>258</v>
-      </c>
-      <c r="G82" t="s">
         <v>258</v>
       </c>
       <c r="H82" t="s">
@@ -11723,9 +11384,6 @@
       <c r="A83" t="s">
         <v>94</v>
       </c>
-      <c r="B83" t="s">
-        <v>258</v>
-      </c>
       <c r="C83" t="s">
         <v>258</v>
       </c>
@@ -11733,9 +11391,6 @@
         <v>258</v>
       </c>
       <c r="E83" t="s">
-        <v>258</v>
-      </c>
-      <c r="F83" t="s">
         <v>258</v>
       </c>
       <c r="G83" t="s">
@@ -11812,9 +11467,6 @@
       <c r="D84" t="s">
         <v>258</v>
       </c>
-      <c r="E84" t="s">
-        <v>258</v>
-      </c>
       <c r="G84" t="s">
         <v>258</v>
       </c>
@@ -11874,9 +11526,6 @@
       <c r="A85" t="s">
         <v>96</v>
       </c>
-      <c r="B85" t="s">
-        <v>258</v>
-      </c>
       <c r="C85" t="s">
         <v>258</v>
       </c>
@@ -11945,9 +11594,6 @@
       <c r="A86" t="s">
         <v>97</v>
       </c>
-      <c r="B86" t="s">
-        <v>258</v>
-      </c>
       <c r="D86" t="s">
         <v>258</v>
       </c>
@@ -12010,13 +11656,7 @@
       <c r="A87" t="s">
         <v>98</v>
       </c>
-      <c r="B87" t="s">
-        <v>258</v>
-      </c>
       <c r="D87" t="s">
-        <v>258</v>
-      </c>
-      <c r="E87" t="s">
         <v>258</v>
       </c>
       <c r="G87" t="s">
@@ -12084,9 +11724,6 @@
       <c r="A88" t="s">
         <v>99</v>
       </c>
-      <c r="B88" t="s">
-        <v>258</v>
-      </c>
       <c r="H88" t="s">
         <v>258</v>
       </c>
@@ -12143,9 +11780,6 @@
       <c r="A89" t="s">
         <v>100</v>
       </c>
-      <c r="B89" t="s">
-        <v>258</v>
-      </c>
       <c r="C89" t="s">
         <v>258</v>
       </c>
@@ -12208,16 +11842,10 @@
       <c r="A90" t="s">
         <v>101</v>
       </c>
-      <c r="B90" t="s">
-        <v>258</v>
-      </c>
       <c r="C90" t="s">
         <v>258</v>
       </c>
       <c r="D90" t="s">
-        <v>258</v>
-      </c>
-      <c r="E90" t="s">
         <v>258</v>
       </c>
       <c r="G90" t="s">
@@ -12353,9 +11981,6 @@
       <c r="A92" t="s">
         <v>103</v>
       </c>
-      <c r="B92" t="s">
-        <v>258</v>
-      </c>
       <c r="C92" t="s">
         <v>258</v>
       </c>
@@ -12415,9 +12040,6 @@
       <c r="A93" t="s">
         <v>104</v>
       </c>
-      <c r="B93" t="s">
-        <v>258</v>
-      </c>
       <c r="C93" t="s">
         <v>258</v>
       </c>
@@ -12554,13 +12176,7 @@
       <c r="A95" t="s">
         <v>106</v>
       </c>
-      <c r="B95" t="s">
-        <v>258</v>
-      </c>
       <c r="D95" t="s">
-        <v>258</v>
-      </c>
-      <c r="E95" t="s">
         <v>258</v>
       </c>
       <c r="G95" t="s">
@@ -12628,9 +12244,6 @@
       <c r="A96" t="s">
         <v>107</v>
       </c>
-      <c r="B96" t="s">
-        <v>258</v>
-      </c>
       <c r="D96" t="s">
         <v>258</v>
       </c>
@@ -12690,16 +12303,10 @@
       <c r="A97" t="s">
         <v>108</v>
       </c>
-      <c r="B97" t="s">
-        <v>258</v>
-      </c>
       <c r="E97" t="s">
         <v>258</v>
       </c>
       <c r="F97" t="s">
-        <v>258</v>
-      </c>
-      <c r="G97" t="s">
         <v>258</v>
       </c>
       <c r="H97" t="s">
@@ -12758,9 +12365,6 @@
       <c r="A98" t="s">
         <v>109</v>
       </c>
-      <c r="B98" t="s">
-        <v>258</v>
-      </c>
       <c r="D98" t="s">
         <v>258</v>
       </c>
@@ -12811,16 +12415,10 @@
       <c r="A99" t="s">
         <v>110</v>
       </c>
-      <c r="B99" t="s">
-        <v>258</v>
-      </c>
       <c r="C99" t="s">
         <v>258</v>
       </c>
       <c r="D99" t="s">
-        <v>258</v>
-      </c>
-      <c r="E99" t="s">
         <v>258</v>
       </c>
       <c r="G99" t="s">
@@ -12897,9 +12495,6 @@
       <c r="D100" t="s">
         <v>258</v>
       </c>
-      <c r="E100" t="s">
-        <v>258</v>
-      </c>
       <c r="G100" t="s">
         <v>258</v>
       </c>
@@ -12956,16 +12551,10 @@
       <c r="A101" t="s">
         <v>112</v>
       </c>
-      <c r="B101" t="s">
-        <v>258</v>
-      </c>
       <c r="C101" t="s">
         <v>258</v>
       </c>
       <c r="D101" t="s">
-        <v>258</v>
-      </c>
-      <c r="F101" t="s">
         <v>258</v>
       </c>
       <c r="H101" t="s">
@@ -13030,9 +12619,6 @@
       <c r="A102" t="s">
         <v>113</v>
       </c>
-      <c r="B102" t="s">
-        <v>258</v>
-      </c>
       <c r="C102" t="s">
         <v>258</v>
       </c>
@@ -13104,16 +12690,10 @@
       <c r="A103" t="s">
         <v>114</v>
       </c>
-      <c r="B103" t="s">
-        <v>258</v>
-      </c>
       <c r="C103" t="s">
         <v>258</v>
       </c>
       <c r="D103" t="s">
-        <v>258</v>
-      </c>
-      <c r="E103" t="s">
         <v>258</v>
       </c>
       <c r="G103" t="s">
@@ -13181,16 +12761,10 @@
       <c r="A104" t="s">
         <v>115</v>
       </c>
-      <c r="B104" t="s">
-        <v>258</v>
-      </c>
       <c r="C104" t="s">
         <v>258</v>
       </c>
       <c r="D104" t="s">
-        <v>258</v>
-      </c>
-      <c r="E104" t="s">
         <v>258</v>
       </c>
       <c r="G104" t="s">
@@ -13252,13 +12826,7 @@
       <c r="A105" t="s">
         <v>116</v>
       </c>
-      <c r="B105" t="s">
-        <v>258</v>
-      </c>
       <c r="E105" t="s">
-        <v>258</v>
-      </c>
-      <c r="G105" t="s">
         <v>258</v>
       </c>
       <c r="H105" t="s">
@@ -13311,9 +12879,6 @@
       <c r="A106" t="s">
         <v>117</v>
       </c>
-      <c r="B106" t="s">
-        <v>258</v>
-      </c>
       <c r="C106" t="s">
         <v>258</v>
       </c>
@@ -13435,16 +13000,10 @@
       <c r="A108" t="s">
         <v>119</v>
       </c>
-      <c r="B108" t="s">
-        <v>258</v>
-      </c>
       <c r="C108" t="s">
         <v>258</v>
       </c>
       <c r="D108" t="s">
-        <v>258</v>
-      </c>
-      <c r="E108" t="s">
         <v>258</v>
       </c>
       <c r="G108" t="s">
@@ -13509,19 +13068,10 @@
       <c r="A109" t="s">
         <v>120</v>
       </c>
-      <c r="B109" t="s">
-        <v>258</v>
-      </c>
       <c r="C109" t="s">
         <v>258</v>
       </c>
       <c r="D109" t="s">
-        <v>258</v>
-      </c>
-      <c r="E109" t="s">
-        <v>258</v>
-      </c>
-      <c r="G109" t="s">
         <v>258</v>
       </c>
       <c r="H109" t="s">
@@ -13589,16 +13139,10 @@
       <c r="A110" t="s">
         <v>121</v>
       </c>
-      <c r="B110" t="s">
-        <v>258</v>
-      </c>
       <c r="C110" t="s">
         <v>258</v>
       </c>
       <c r="D110" t="s">
-        <v>258</v>
-      </c>
-      <c r="E110" t="s">
         <v>258</v>
       </c>
       <c r="G110" t="s">
@@ -13734,16 +13278,10 @@
       <c r="A112" t="s">
         <v>123</v>
       </c>
-      <c r="B112" t="s">
-        <v>258</v>
-      </c>
       <c r="C112" t="s">
         <v>258</v>
       </c>
       <c r="D112" t="s">
-        <v>258</v>
-      </c>
-      <c r="E112" t="s">
         <v>258</v>
       </c>
       <c r="F112" t="s">
@@ -13814,16 +13352,10 @@
       <c r="A113" t="s">
         <v>124</v>
       </c>
-      <c r="B113" t="s">
-        <v>258</v>
-      </c>
       <c r="C113" t="s">
         <v>258</v>
       </c>
       <c r="D113" t="s">
-        <v>258</v>
-      </c>
-      <c r="E113" t="s">
         <v>258</v>
       </c>
       <c r="G113" t="s">
@@ -13891,16 +13423,7 @@
       <c r="A114" t="s">
         <v>125</v>
       </c>
-      <c r="B114" t="s">
-        <v>258</v>
-      </c>
       <c r="D114" t="s">
-        <v>258</v>
-      </c>
-      <c r="E114" t="s">
-        <v>258</v>
-      </c>
-      <c r="F114" t="s">
         <v>258</v>
       </c>
       <c r="G114" t="s">
@@ -13962,19 +13485,10 @@
       <c r="A115" t="s">
         <v>126</v>
       </c>
-      <c r="B115" t="s">
-        <v>258</v>
-      </c>
       <c r="C115" t="s">
         <v>258</v>
       </c>
       <c r="D115" t="s">
-        <v>258</v>
-      </c>
-      <c r="E115" t="s">
-        <v>258</v>
-      </c>
-      <c r="F115" t="s">
         <v>258</v>
       </c>
       <c r="G115" t="s">
@@ -14135,13 +13649,7 @@
       <c r="C2" t="s">
         <v>258</v>
       </c>
-      <c r="D2" t="s">
-        <v>258</v>
-      </c>
       <c r="E2" t="s">
-        <v>258</v>
-      </c>
-      <c r="G2" t="s">
         <v>258</v>
       </c>
       <c r="K2" t="s">
@@ -14250,16 +13758,10 @@
       <c r="C4" t="s">
         <v>258</v>
       </c>
-      <c r="D4" t="s">
-        <v>258</v>
-      </c>
       <c r="E4" t="s">
         <v>258</v>
       </c>
       <c r="F4" t="s">
-        <v>258</v>
-      </c>
-      <c r="G4" t="s">
         <v>258</v>
       </c>
       <c r="H4" t="s">
@@ -14321,16 +13823,10 @@
       <c r="C5" t="s">
         <v>258</v>
       </c>
-      <c r="D5" t="s">
-        <v>258</v>
-      </c>
       <c r="E5" t="s">
         <v>258</v>
       </c>
       <c r="F5" t="s">
-        <v>258</v>
-      </c>
-      <c r="G5" t="s">
         <v>258</v>
       </c>
       <c r="H5" t="s">
@@ -14407,9 +13903,6 @@
       <c r="F6" t="s">
         <v>258</v>
       </c>
-      <c r="G6" t="s">
-        <v>258</v>
-      </c>
       <c r="H6" t="s">
         <v>258</v>
       </c>
@@ -14438,9 +13931,6 @@
         <v>258</v>
       </c>
       <c r="Q6" t="s">
-        <v>258</v>
-      </c>
-      <c r="R6" t="s">
         <v>258</v>
       </c>
       <c r="S6" t="s">
@@ -14540,9 +14030,6 @@
       <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
-        <v>258</v>
-      </c>
       <c r="D8" t="s">
         <v>258</v>
       </c>
@@ -14550,9 +14037,6 @@
         <v>258</v>
       </c>
       <c r="F8" t="s">
-        <v>258</v>
-      </c>
-      <c r="G8" t="s">
         <v>258</v>
       </c>
       <c r="H8" t="s">
@@ -14623,9 +14107,6 @@
       <c r="F9" t="s">
         <v>258</v>
       </c>
-      <c r="G9" t="s">
-        <v>258</v>
-      </c>
       <c r="H9" t="s">
         <v>258</v>
       </c>
@@ -14685,16 +14166,10 @@
       <c r="C10" t="s">
         <v>258</v>
       </c>
-      <c r="D10" t="s">
-        <v>258</v>
-      </c>
       <c r="E10" t="s">
         <v>258</v>
       </c>
       <c r="F10" t="s">
-        <v>258</v>
-      </c>
-      <c r="G10" t="s">
         <v>258</v>
       </c>
       <c r="K10" t="s">
@@ -14791,9 +14266,6 @@
       <c r="E12" t="s">
         <v>258</v>
       </c>
-      <c r="G12" t="s">
-        <v>258</v>
-      </c>
       <c r="H12" t="s">
         <v>258</v>
       </c>
@@ -14865,9 +14337,6 @@
       <c r="F13" t="s">
         <v>258</v>
       </c>
-      <c r="G13" t="s">
-        <v>258</v>
-      </c>
       <c r="K13" t="s">
         <v>258</v>
       </c>
@@ -14971,16 +14440,10 @@
       <c r="C15" t="s">
         <v>258</v>
       </c>
-      <c r="D15" t="s">
-        <v>258</v>
-      </c>
       <c r="E15" t="s">
         <v>258</v>
       </c>
       <c r="F15" t="s">
-        <v>258</v>
-      </c>
-      <c r="G15" t="s">
         <v>258</v>
       </c>
       <c r="H15" t="s">
@@ -15075,9 +14538,6 @@
       <c r="Q16" t="s">
         <v>258</v>
       </c>
-      <c r="R16" t="s">
-        <v>258</v>
-      </c>
       <c r="S16" t="s">
         <v>258</v>
       </c>
@@ -15110,16 +14570,10 @@
       <c r="C17" t="s">
         <v>258</v>
       </c>
-      <c r="D17" t="s">
-        <v>258</v>
-      </c>
       <c r="E17" t="s">
         <v>258</v>
       </c>
       <c r="F17" t="s">
-        <v>258</v>
-      </c>
-      <c r="G17" t="s">
         <v>258</v>
       </c>
       <c r="H17" t="s">
@@ -15243,9 +14697,6 @@
       <c r="A19" t="s">
         <v>25</v>
       </c>
-      <c r="C19" t="s">
-        <v>258</v>
-      </c>
       <c r="D19" t="s">
         <v>258</v>
       </c>
@@ -15253,9 +14704,6 @@
         <v>258</v>
       </c>
       <c r="F19" t="s">
-        <v>258</v>
-      </c>
-      <c r="G19" t="s">
         <v>258</v>
       </c>
       <c r="H19" t="s">
@@ -15305,9 +14753,6 @@
       <c r="F20" t="s">
         <v>258</v>
       </c>
-      <c r="G20" t="s">
-        <v>258</v>
-      </c>
       <c r="H20" t="s">
         <v>258</v>
       </c>
@@ -15376,9 +14821,6 @@
       <c r="F21" t="s">
         <v>258</v>
       </c>
-      <c r="G21" t="s">
-        <v>258</v>
-      </c>
       <c r="H21" t="s">
         <v>258</v>
       </c>
@@ -15444,16 +14886,10 @@
       <c r="C22" t="s">
         <v>258</v>
       </c>
-      <c r="D22" t="s">
-        <v>258</v>
-      </c>
       <c r="E22" t="s">
         <v>258</v>
       </c>
       <c r="F22" t="s">
-        <v>258</v>
-      </c>
-      <c r="G22" t="s">
         <v>258</v>
       </c>
       <c r="H22" t="s">
@@ -15515,19 +14951,10 @@
       <c r="B23" t="s">
         <v>258</v>
       </c>
-      <c r="C23" t="s">
-        <v>258</v>
-      </c>
-      <c r="D23" t="s">
-        <v>258</v>
-      </c>
       <c r="E23" t="s">
         <v>258</v>
       </c>
       <c r="F23" t="s">
-        <v>258</v>
-      </c>
-      <c r="G23" t="s">
         <v>258</v>
       </c>
       <c r="H23" t="s">
@@ -15601,9 +15028,6 @@
       <c r="F24" t="s">
         <v>258</v>
       </c>
-      <c r="G24" t="s">
-        <v>258</v>
-      </c>
       <c r="H24" t="s">
         <v>258</v>
       </c>
@@ -15660,16 +15084,10 @@
       <c r="C25" t="s">
         <v>258</v>
       </c>
-      <c r="D25" t="s">
-        <v>258</v>
-      </c>
       <c r="E25" t="s">
         <v>258</v>
       </c>
       <c r="F25" t="s">
-        <v>258</v>
-      </c>
-      <c r="G25" t="s">
         <v>258</v>
       </c>
       <c r="H25" t="s">
@@ -15737,16 +15155,10 @@
       <c r="C26" t="s">
         <v>258</v>
       </c>
-      <c r="D26" t="s">
-        <v>258</v>
-      </c>
       <c r="E26" t="s">
         <v>258</v>
       </c>
       <c r="F26" t="s">
-        <v>258</v>
-      </c>
-      <c r="G26" t="s">
         <v>258</v>
       </c>
       <c r="H26" t="s">
@@ -15799,9 +15211,6 @@
       <c r="A27" t="s">
         <v>34</v>
       </c>
-      <c r="C27" t="s">
-        <v>258</v>
-      </c>
       <c r="D27" t="s">
         <v>258</v>
       </c>
@@ -15873,9 +15282,6 @@
       <c r="F28" t="s">
         <v>258</v>
       </c>
-      <c r="G28" t="s">
-        <v>258</v>
-      </c>
       <c r="H28" t="s">
         <v>258</v>
       </c>
@@ -15935,19 +15341,10 @@
       <c r="B29" t="s">
         <v>258</v>
       </c>
-      <c r="C29" t="s">
-        <v>258</v>
-      </c>
-      <c r="D29" t="s">
-        <v>258</v>
-      </c>
       <c r="E29" t="s">
         <v>258</v>
       </c>
       <c r="F29" t="s">
-        <v>258</v>
-      </c>
-      <c r="G29" t="s">
         <v>258</v>
       </c>
       <c r="H29" t="s">
@@ -16018,9 +15415,6 @@
       <c r="F30" t="s">
         <v>258</v>
       </c>
-      <c r="G30" t="s">
-        <v>258</v>
-      </c>
       <c r="H30" t="s">
         <v>258</v>
       </c>
@@ -16077,16 +15471,10 @@
       <c r="C31" t="s">
         <v>258</v>
       </c>
-      <c r="D31" t="s">
-        <v>258</v>
-      </c>
       <c r="E31" t="s">
         <v>258</v>
       </c>
       <c r="F31" t="s">
-        <v>258</v>
-      </c>
-      <c r="G31" t="s">
         <v>258</v>
       </c>
       <c r="K31" t="s">
@@ -16130,21 +15518,12 @@
       <c r="B32" t="s">
         <v>258</v>
       </c>
-      <c r="C32" t="s">
-        <v>258</v>
-      </c>
-      <c r="D32" t="s">
-        <v>258</v>
-      </c>
       <c r="E32" t="s">
         <v>258</v>
       </c>
       <c r="F32" t="s">
         <v>258</v>
       </c>
-      <c r="G32" t="s">
-        <v>258</v>
-      </c>
       <c r="H32" t="s">
         <v>258</v>
       </c>
@@ -16173,9 +15552,6 @@
         <v>258</v>
       </c>
       <c r="Q32" t="s">
-        <v>258</v>
-      </c>
-      <c r="R32" t="s">
         <v>258</v>
       </c>
       <c r="S32" t="s">
@@ -16213,16 +15589,10 @@
       <c r="C33" t="s">
         <v>258</v>
       </c>
-      <c r="D33" t="s">
-        <v>258</v>
-      </c>
       <c r="E33" t="s">
         <v>258</v>
       </c>
       <c r="F33" t="s">
-        <v>258</v>
-      </c>
-      <c r="G33" t="s">
         <v>258</v>
       </c>
       <c r="H33" t="s">
@@ -16284,9 +15654,6 @@
       <c r="C34" t="s">
         <v>258</v>
       </c>
-      <c r="D34" t="s">
-        <v>258</v>
-      </c>
       <c r="E34" t="s">
         <v>258</v>
       </c>
@@ -16361,9 +15728,6 @@
       <c r="F35" t="s">
         <v>258</v>
       </c>
-      <c r="G35" t="s">
-        <v>258</v>
-      </c>
       <c r="H35" t="s">
         <v>258</v>
       </c>
@@ -16426,9 +15790,6 @@
       <c r="F36" t="s">
         <v>258</v>
       </c>
-      <c r="G36" t="s">
-        <v>258</v>
-      </c>
       <c r="H36" t="s">
         <v>258</v>
       </c>
@@ -16479,9 +15840,6 @@
       <c r="F37" t="s">
         <v>258</v>
       </c>
-      <c r="G37" t="s">
-        <v>258</v>
-      </c>
       <c r="H37" t="s">
         <v>258</v>
       </c>
@@ -16544,16 +15902,10 @@
       <c r="C38" t="s">
         <v>258</v>
       </c>
-      <c r="D38" t="s">
-        <v>258</v>
-      </c>
       <c r="E38" t="s">
         <v>258</v>
       </c>
       <c r="F38" t="s">
-        <v>258</v>
-      </c>
-      <c r="G38" t="s">
         <v>258</v>
       </c>
       <c r="H38" t="s">
@@ -16606,9 +15958,6 @@
       <c r="A39" t="s">
         <v>46</v>
       </c>
-      <c r="C39" t="s">
-        <v>258</v>
-      </c>
       <c r="D39" t="s">
         <v>258</v>
       </c>
@@ -16616,9 +15965,6 @@
         <v>258</v>
       </c>
       <c r="F39" t="s">
-        <v>258</v>
-      </c>
-      <c r="G39" t="s">
         <v>258</v>
       </c>
       <c r="H39" t="s">
@@ -16683,16 +16029,10 @@
       <c r="C40" t="s">
         <v>258</v>
       </c>
-      <c r="D40" t="s">
-        <v>258</v>
-      </c>
       <c r="E40" t="s">
         <v>258</v>
       </c>
       <c r="F40" t="s">
-        <v>258</v>
-      </c>
-      <c r="G40" t="s">
         <v>258</v>
       </c>
       <c r="H40" t="s">
@@ -16798,9 +16138,6 @@
       <c r="F42" t="s">
         <v>258</v>
       </c>
-      <c r="G42" t="s">
-        <v>258</v>
-      </c>
       <c r="H42" t="s">
         <v>258</v>
       </c>
@@ -16898,9 +16235,6 @@
       <c r="E44" t="s">
         <v>258</v>
       </c>
-      <c r="G44" t="s">
-        <v>258</v>
-      </c>
       <c r="N44" t="s">
         <v>258</v>
       </c>
@@ -16939,9 +16273,6 @@
       <c r="F45" t="s">
         <v>258</v>
       </c>
-      <c r="G45" t="s">
-        <v>258</v>
-      </c>
       <c r="H45" t="s">
         <v>258</v>
       </c>
@@ -17004,9 +16335,6 @@
       <c r="E46" t="s">
         <v>258</v>
       </c>
-      <c r="G46" t="s">
-        <v>258</v>
-      </c>
       <c r="N46" t="s">
         <v>258</v>
       </c>
@@ -17014,9 +16342,6 @@
         <v>258</v>
       </c>
       <c r="Q46" t="s">
-        <v>258</v>
-      </c>
-      <c r="R46" t="s">
         <v>258</v>
       </c>
       <c r="S46" t="s">
@@ -17045,9 +16370,6 @@
       <c r="F47" t="s">
         <v>258</v>
       </c>
-      <c r="G47" t="s">
-        <v>258</v>
-      </c>
       <c r="I47" t="s">
         <v>258</v>
       </c>
@@ -17110,9 +16432,6 @@
       <c r="F48" t="s">
         <v>258</v>
       </c>
-      <c r="G48" t="s">
-        <v>258</v>
-      </c>
       <c r="H48" t="s">
         <v>258</v>
       </c>
@@ -17196,9 +16515,6 @@
       <c r="Q49" t="s">
         <v>258</v>
       </c>
-      <c r="R49" t="s">
-        <v>258</v>
-      </c>
       <c r="S49" t="s">
         <v>258</v>
       </c>
@@ -17228,9 +16544,6 @@
       <c r="A50" t="s">
         <v>58</v>
       </c>
-      <c r="C50" t="s">
-        <v>258</v>
-      </c>
       <c r="D50" t="s">
         <v>258</v>
       </c>
@@ -17238,9 +16551,6 @@
         <v>258</v>
       </c>
       <c r="F50" t="s">
-        <v>258</v>
-      </c>
-      <c r="G50" t="s">
         <v>258</v>
       </c>
       <c r="H50" t="s">
@@ -17308,16 +16618,10 @@
       <c r="C51" t="s">
         <v>258</v>
       </c>
-      <c r="D51" t="s">
-        <v>258</v>
-      </c>
       <c r="E51" t="s">
         <v>258</v>
       </c>
       <c r="F51" t="s">
-        <v>258</v>
-      </c>
-      <c r="G51" t="s">
         <v>258</v>
       </c>
       <c r="H51" t="s">
@@ -17379,16 +16683,10 @@
       <c r="C52" t="s">
         <v>258</v>
       </c>
-      <c r="D52" t="s">
-        <v>258</v>
-      </c>
       <c r="E52" t="s">
         <v>258</v>
       </c>
       <c r="F52" t="s">
-        <v>258</v>
-      </c>
-      <c r="G52" t="s">
         <v>258</v>
       </c>
       <c r="H52" t="s">
@@ -17500,16 +16798,10 @@
       <c r="C54" t="s">
         <v>258</v>
       </c>
-      <c r="D54" t="s">
-        <v>258</v>
-      </c>
       <c r="E54" t="s">
         <v>258</v>
       </c>
       <c r="F54" t="s">
-        <v>258</v>
-      </c>
-      <c r="G54" t="s">
         <v>258</v>
       </c>
       <c r="H54" t="s">
@@ -17577,16 +16869,10 @@
       <c r="C55" t="s">
         <v>258</v>
       </c>
-      <c r="D55" t="s">
-        <v>258</v>
-      </c>
       <c r="E55" t="s">
         <v>258</v>
       </c>
       <c r="F55" t="s">
-        <v>258</v>
-      </c>
-      <c r="G55" t="s">
         <v>258</v>
       </c>
       <c r="H55" t="s">
@@ -17636,9 +16922,6 @@
       <c r="F56" t="s">
         <v>258</v>
       </c>
-      <c r="G56" t="s">
-        <v>258</v>
-      </c>
       <c r="H56" t="s">
         <v>258</v>
       </c>
@@ -17652,9 +16935,6 @@
         <v>258</v>
       </c>
       <c r="Q56" t="s">
-        <v>258</v>
-      </c>
-      <c r="R56" t="s">
         <v>258</v>
       </c>
       <c r="S56" t="s">
@@ -17689,9 +16969,6 @@
       <c r="F57" t="s">
         <v>258</v>
       </c>
-      <c r="G57" t="s">
-        <v>258</v>
-      </c>
       <c r="H57" t="s">
         <v>258</v>
       </c>
@@ -17760,9 +17037,6 @@
       <c r="F58" t="s">
         <v>258</v>
       </c>
-      <c r="G58" t="s">
-        <v>258</v>
-      </c>
       <c r="H58" t="s">
         <v>258</v>
       </c>
@@ -17881,16 +17155,10 @@
       <c r="C60" t="s">
         <v>258</v>
       </c>
-      <c r="D60" t="s">
-        <v>258</v>
-      </c>
       <c r="E60" t="s">
         <v>258</v>
       </c>
       <c r="F60" t="s">
-        <v>258</v>
-      </c>
-      <c r="G60" t="s">
         <v>258</v>
       </c>
       <c r="H60" t="s">
@@ -17955,9 +17223,6 @@
       <c r="F61" t="s">
         <v>258</v>
       </c>
-      <c r="G61" t="s">
-        <v>258</v>
-      </c>
       <c r="H61" t="s">
         <v>258</v>
       </c>
@@ -18014,9 +17279,6 @@
       <c r="C62" t="s">
         <v>258</v>
       </c>
-      <c r="D62" t="s">
-        <v>258</v>
-      </c>
       <c r="E62" t="s">
         <v>258</v>
       </c>
@@ -18082,9 +17344,6 @@
       <c r="C63" t="s">
         <v>258</v>
       </c>
-      <c r="D63" t="s">
-        <v>258</v>
-      </c>
       <c r="E63" t="s">
         <v>258</v>
       </c>
@@ -18144,16 +17403,10 @@
       <c r="C64" t="s">
         <v>258</v>
       </c>
-      <c r="D64" t="s">
-        <v>258</v>
-      </c>
       <c r="E64" t="s">
         <v>258</v>
       </c>
       <c r="F64" t="s">
-        <v>258</v>
-      </c>
-      <c r="G64" t="s">
         <v>258</v>
       </c>
       <c r="H64" t="s">
@@ -18224,9 +17477,6 @@
       <c r="F65" t="s">
         <v>258</v>
       </c>
-      <c r="G65" t="s">
-        <v>258</v>
-      </c>
       <c r="H65" t="s">
         <v>258</v>
       </c>
@@ -18283,16 +17533,10 @@
       <c r="C66" t="s">
         <v>258</v>
       </c>
-      <c r="D66" t="s">
-        <v>258</v>
-      </c>
       <c r="E66" t="s">
         <v>258</v>
       </c>
       <c r="F66" t="s">
-        <v>258</v>
-      </c>
-      <c r="G66" t="s">
         <v>258</v>
       </c>
       <c r="H66" t="s">
@@ -18354,9 +17598,6 @@
       <c r="C67" t="s">
         <v>258</v>
       </c>
-      <c r="D67" t="s">
-        <v>258</v>
-      </c>
       <c r="P67" t="s">
         <v>258</v>
       </c>
@@ -18386,16 +17627,10 @@
       <c r="C68" t="s">
         <v>258</v>
       </c>
-      <c r="D68" t="s">
-        <v>258</v>
-      </c>
       <c r="E68" t="s">
         <v>258</v>
       </c>
       <c r="F68" t="s">
-        <v>258</v>
-      </c>
-      <c r="G68" t="s">
         <v>258</v>
       </c>
       <c r="H68" t="s">
@@ -18487,9 +17722,6 @@
       <c r="Q69" t="s">
         <v>258</v>
       </c>
-      <c r="R69" t="s">
-        <v>258</v>
-      </c>
       <c r="S69" t="s">
         <v>258</v>
       </c>
@@ -18575,9 +17807,6 @@
       <c r="A71" t="s">
         <v>82</v>
       </c>
-      <c r="C71" t="s">
-        <v>258</v>
-      </c>
       <c r="D71" t="s">
         <v>258</v>
       </c>
@@ -18594,9 +17823,6 @@
         <v>258</v>
       </c>
       <c r="Q71" t="s">
-        <v>258</v>
-      </c>
-      <c r="R71" t="s">
         <v>258</v>
       </c>
       <c r="S71" t="s">
@@ -18622,9 +17848,6 @@
       <c r="C72" t="s">
         <v>258</v>
       </c>
-      <c r="D72" t="s">
-        <v>258</v>
-      </c>
       <c r="E72" t="s">
         <v>258</v>
       </c>
@@ -18690,9 +17913,6 @@
       <c r="C73" t="s">
         <v>258</v>
       </c>
-      <c r="D73" t="s">
-        <v>258</v>
-      </c>
       <c r="E73" t="s">
         <v>258</v>
       </c>
@@ -18764,9 +17984,6 @@
       <c r="F74" t="s">
         <v>258</v>
       </c>
-      <c r="G74" t="s">
-        <v>258</v>
-      </c>
       <c r="H74" t="s">
         <v>258</v>
       </c>
@@ -18832,16 +18049,10 @@
       <c r="C75" t="s">
         <v>258</v>
       </c>
-      <c r="D75" t="s">
-        <v>258</v>
-      </c>
       <c r="E75" t="s">
         <v>258</v>
       </c>
       <c r="F75" t="s">
-        <v>258</v>
-      </c>
-      <c r="G75" t="s">
         <v>258</v>
       </c>
       <c r="H75" t="s">
@@ -18903,9 +18114,6 @@
       <c r="C76" t="s">
         <v>258</v>
       </c>
-      <c r="D76" t="s">
-        <v>258</v>
-      </c>
       <c r="E76" t="s">
         <v>258</v>
       </c>
@@ -18997,21 +18205,12 @@
       <c r="B78" t="s">
         <v>258</v>
       </c>
-      <c r="C78" t="s">
-        <v>258</v>
-      </c>
-      <c r="D78" t="s">
-        <v>258</v>
-      </c>
       <c r="E78" t="s">
         <v>258</v>
       </c>
       <c r="F78" t="s">
         <v>258</v>
       </c>
-      <c r="G78" t="s">
-        <v>258</v>
-      </c>
       <c r="H78" t="s">
         <v>258</v>
       </c>
@@ -19040,9 +18239,6 @@
         <v>258</v>
       </c>
       <c r="Q78" t="s">
-        <v>258</v>
-      </c>
-      <c r="R78" t="s">
         <v>258</v>
       </c>
       <c r="S78" t="s">
@@ -19083,9 +18279,6 @@
       <c r="F79" t="s">
         <v>258</v>
       </c>
-      <c r="G79" t="s">
-        <v>258</v>
-      </c>
       <c r="H79" t="s">
         <v>258</v>
       </c>
@@ -19151,9 +18344,6 @@
       <c r="F80" t="s">
         <v>258</v>
       </c>
-      <c r="G80" t="s">
-        <v>258</v>
-      </c>
       <c r="H80" t="s">
         <v>258</v>
       </c>
@@ -19213,16 +18403,10 @@
       <c r="C81" t="s">
         <v>258</v>
       </c>
-      <c r="D81" t="s">
-        <v>258</v>
-      </c>
       <c r="E81" t="s">
         <v>258</v>
       </c>
       <c r="F81" t="s">
-        <v>258</v>
-      </c>
-      <c r="G81" t="s">
         <v>258</v>
       </c>
       <c r="H81" t="s">
@@ -19284,19 +18468,10 @@
       <c r="B82" t="s">
         <v>258</v>
       </c>
-      <c r="C82" t="s">
-        <v>258</v>
-      </c>
-      <c r="D82" t="s">
-        <v>258</v>
-      </c>
       <c r="E82" t="s">
         <v>258</v>
       </c>
       <c r="F82" t="s">
-        <v>258</v>
-      </c>
-      <c r="G82" t="s">
         <v>258</v>
       </c>
       <c r="H82" t="s">
@@ -19370,9 +18545,6 @@
       <c r="F83" t="s">
         <v>258</v>
       </c>
-      <c r="G83" t="s">
-        <v>258</v>
-      </c>
       <c r="H83" t="s">
         <v>258</v>
       </c>
@@ -19401,9 +18573,6 @@
         <v>258</v>
       </c>
       <c r="Q83" t="s">
-        <v>258</v>
-      </c>
-      <c r="R83" t="s">
         <v>258</v>
       </c>
       <c r="S83" t="s">
@@ -19441,9 +18610,6 @@
       <c r="C84" t="s">
         <v>258</v>
       </c>
-      <c r="D84" t="s">
-        <v>258</v>
-      </c>
       <c r="E84" t="s">
         <v>258</v>
       </c>
@@ -19515,9 +18681,6 @@
       <c r="F85" t="s">
         <v>258</v>
       </c>
-      <c r="G85" t="s">
-        <v>258</v>
-      </c>
       <c r="H85" t="s">
         <v>258</v>
       </c>
@@ -19586,9 +18749,6 @@
       <c r="F86" t="s">
         <v>258</v>
       </c>
-      <c r="G86" t="s">
-        <v>258</v>
-      </c>
       <c r="H86" t="s">
         <v>258</v>
       </c>
@@ -19648,16 +18808,10 @@
       <c r="C87" t="s">
         <v>258</v>
       </c>
-      <c r="D87" t="s">
-        <v>258</v>
-      </c>
       <c r="E87" t="s">
         <v>258</v>
       </c>
       <c r="F87" t="s">
-        <v>258</v>
-      </c>
-      <c r="G87" t="s">
         <v>258</v>
       </c>
       <c r="H87" t="s">
@@ -19725,9 +18879,6 @@
       <c r="F88" t="s">
         <v>258</v>
       </c>
-      <c r="G88" t="s">
-        <v>258</v>
-      </c>
       <c r="H88" t="s">
         <v>258</v>
       </c>
@@ -19784,9 +18935,6 @@
       <c r="F89" t="s">
         <v>258</v>
       </c>
-      <c r="G89" t="s">
-        <v>258</v>
-      </c>
       <c r="H89" t="s">
         <v>258</v>
       </c>
@@ -19846,16 +18994,10 @@
       <c r="C90" t="s">
         <v>258</v>
       </c>
-      <c r="D90" t="s">
-        <v>258</v>
-      </c>
       <c r="E90" t="s">
         <v>258</v>
       </c>
       <c r="F90" t="s">
-        <v>258</v>
-      </c>
-      <c r="G90" t="s">
         <v>258</v>
       </c>
       <c r="H90" t="s">
@@ -19994,9 +19136,6 @@
       <c r="F92" t="s">
         <v>258</v>
       </c>
-      <c r="G92" t="s">
-        <v>258</v>
-      </c>
       <c r="H92" t="s">
         <v>258</v>
       </c>
@@ -20062,9 +19201,6 @@
       <c r="F93" t="s">
         <v>258</v>
       </c>
-      <c r="G93" t="s">
-        <v>258</v>
-      </c>
       <c r="H93" t="s">
         <v>258</v>
       </c>
@@ -20192,16 +19328,10 @@
       <c r="C95" t="s">
         <v>258</v>
       </c>
-      <c r="D95" t="s">
-        <v>258</v>
-      </c>
       <c r="E95" t="s">
         <v>258</v>
       </c>
       <c r="F95" t="s">
-        <v>258</v>
-      </c>
-      <c r="G95" t="s">
         <v>258</v>
       </c>
       <c r="H95" t="s">
@@ -20269,9 +19399,6 @@
       <c r="F96" t="s">
         <v>258</v>
       </c>
-      <c r="G96" t="s">
-        <v>258</v>
-      </c>
       <c r="H96" t="s">
         <v>258</v>
       </c>
@@ -20325,16 +19452,10 @@
       <c r="A97" t="s">
         <v>108</v>
       </c>
-      <c r="C97" t="s">
-        <v>258</v>
-      </c>
       <c r="D97" t="s">
         <v>258</v>
       </c>
       <c r="E97" t="s">
-        <v>258</v>
-      </c>
-      <c r="G97" t="s">
         <v>258</v>
       </c>
       <c r="H97" t="s">
@@ -20396,9 +19517,6 @@
       <c r="E98" t="s">
         <v>258</v>
       </c>
-      <c r="G98" t="s">
-        <v>258</v>
-      </c>
       <c r="H98" t="s">
         <v>258</v>
       </c>
@@ -20449,16 +19567,10 @@
       <c r="C99" t="s">
         <v>258</v>
       </c>
-      <c r="D99" t="s">
-        <v>258</v>
-      </c>
       <c r="E99" t="s">
         <v>258</v>
       </c>
       <c r="F99" t="s">
-        <v>258</v>
-      </c>
-      <c r="G99" t="s">
         <v>258</v>
       </c>
       <c r="H99" t="s">
@@ -20526,9 +19638,6 @@
       <c r="C100" t="s">
         <v>258</v>
       </c>
-      <c r="D100" t="s">
-        <v>258</v>
-      </c>
       <c r="E100" t="s">
         <v>258</v>
       </c>
@@ -20597,9 +19706,6 @@
       <c r="F101" t="s">
         <v>258</v>
       </c>
-      <c r="G101" t="s">
-        <v>258</v>
-      </c>
       <c r="H101" t="s">
         <v>258</v>
       </c>
@@ -20628,9 +19734,6 @@
         <v>258</v>
       </c>
       <c r="Q101" t="s">
-        <v>258</v>
-      </c>
-      <c r="R101" t="s">
         <v>258</v>
       </c>
       <c r="S101" t="s">
@@ -20677,9 +19780,6 @@
       <c r="F102" t="s">
         <v>258</v>
       </c>
-      <c r="G102" t="s">
-        <v>258</v>
-      </c>
       <c r="H102" t="s">
         <v>258</v>
       </c>
@@ -20742,16 +19842,10 @@
       <c r="C103" t="s">
         <v>258</v>
       </c>
-      <c r="D103" t="s">
-        <v>258</v>
-      </c>
       <c r="E103" t="s">
         <v>258</v>
       </c>
       <c r="F103" t="s">
-        <v>258</v>
-      </c>
-      <c r="G103" t="s">
         <v>258</v>
       </c>
       <c r="H103" t="s">
@@ -20819,16 +19913,10 @@
       <c r="C104" t="s">
         <v>258</v>
       </c>
-      <c r="D104" t="s">
-        <v>258</v>
-      </c>
       <c r="E104" t="s">
         <v>258</v>
       </c>
       <c r="F104" t="s">
-        <v>258</v>
-      </c>
-      <c r="G104" t="s">
         <v>258</v>
       </c>
       <c r="H104" t="s">
@@ -20887,16 +19975,10 @@
       <c r="A105" t="s">
         <v>116</v>
       </c>
-      <c r="C105" t="s">
-        <v>258</v>
-      </c>
       <c r="D105" t="s">
         <v>258</v>
       </c>
       <c r="E105" t="s">
-        <v>258</v>
-      </c>
-      <c r="G105" t="s">
         <v>258</v>
       </c>
       <c r="H105" t="s">
@@ -20952,9 +20034,6 @@
       <c r="F106" t="s">
         <v>258</v>
       </c>
-      <c r="G106" t="s">
-        <v>258</v>
-      </c>
       <c r="H106" t="s">
         <v>258</v>
       </c>
@@ -21073,16 +20152,10 @@
       <c r="C108" t="s">
         <v>258</v>
       </c>
-      <c r="D108" t="s">
-        <v>258</v>
-      </c>
       <c r="E108" t="s">
         <v>258</v>
       </c>
       <c r="F108" t="s">
-        <v>258</v>
-      </c>
-      <c r="G108" t="s">
         <v>258</v>
       </c>
       <c r="H108" t="s">
@@ -21147,19 +20220,10 @@
       <c r="B109" t="s">
         <v>258</v>
       </c>
-      <c r="C109" t="s">
-        <v>258</v>
-      </c>
-      <c r="D109" t="s">
-        <v>258</v>
-      </c>
       <c r="E109" t="s">
         <v>258</v>
       </c>
       <c r="F109" t="s">
-        <v>258</v>
-      </c>
-      <c r="G109" t="s">
         <v>258</v>
       </c>
       <c r="H109" t="s">
@@ -21227,16 +20291,10 @@
       <c r="C110" t="s">
         <v>258</v>
       </c>
-      <c r="D110" t="s">
-        <v>258</v>
-      </c>
       <c r="E110" t="s">
         <v>258</v>
       </c>
       <c r="F110" t="s">
-        <v>258</v>
-      </c>
-      <c r="G110" t="s">
         <v>258</v>
       </c>
       <c r="H110" t="s">
@@ -21372,16 +20430,10 @@
       <c r="C112" t="s">
         <v>258</v>
       </c>
-      <c r="D112" t="s">
-        <v>258</v>
-      </c>
       <c r="E112" t="s">
         <v>258</v>
       </c>
       <c r="F112" t="s">
-        <v>258</v>
-      </c>
-      <c r="G112" t="s">
         <v>258</v>
       </c>
       <c r="H112" t="s">
@@ -21452,16 +20504,10 @@
       <c r="C113" t="s">
         <v>258</v>
       </c>
-      <c r="D113" t="s">
-        <v>258</v>
-      </c>
       <c r="E113" t="s">
         <v>258</v>
       </c>
       <c r="F113" t="s">
-        <v>258</v>
-      </c>
-      <c r="G113" t="s">
         <v>258</v>
       </c>
       <c r="H113" t="s">
@@ -21529,15 +20575,9 @@
       <c r="C114" t="s">
         <v>258</v>
       </c>
-      <c r="D114" t="s">
-        <v>258</v>
-      </c>
       <c r="E114" t="s">
         <v>258</v>
       </c>
-      <c r="G114" t="s">
-        <v>258</v>
-      </c>
       <c r="H114" t="s">
         <v>258</v>
       </c>
@@ -21563,9 +20603,6 @@
         <v>258</v>
       </c>
       <c r="Q114" t="s">
-        <v>258</v>
-      </c>
-      <c r="R114" t="s">
         <v>258</v>
       </c>
       <c r="S114" t="s">
@@ -21600,18 +20637,12 @@
       <c r="C115" t="s">
         <v>258</v>
       </c>
-      <c r="D115" t="s">
-        <v>258</v>
-      </c>
       <c r="E115" t="s">
         <v>258</v>
       </c>
       <c r="F115" t="s">
         <v>258</v>
       </c>
-      <c r="G115" t="s">
-        <v>258</v>
-      </c>
       <c r="H115" t="s">
         <v>258</v>
       </c>
@@ -21640,9 +20671,6 @@
         <v>258</v>
       </c>
       <c r="Q115" t="s">
-        <v>258</v>
-      </c>
-      <c r="R115" t="s">
         <v>258</v>
       </c>
       <c r="S115" t="s">
@@ -21690,178 +20718,178 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>6</v>
       </c>
       <c r="C2">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="B3">
         <v>6</v>
       </c>
       <c r="C3">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="B4">
         <v>6</v>
       </c>
       <c r="C4">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="B5">
         <v>6</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="B6">
         <v>6</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="B7">
         <v>6</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>123</v>
+        <v>32</v>
       </c>
       <c r="B8">
         <v>6</v>
       </c>
       <c r="C8">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B9">
         <v>6</v>
       </c>
       <c r="C9">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B10">
         <v>6</v>
       </c>
       <c r="C10">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B11">
         <v>6</v>
       </c>
       <c r="C11">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B12">
         <v>6</v>
       </c>
       <c r="C12">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B13">
         <v>6</v>
       </c>
       <c r="C13">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B14">
         <v>6</v>
       </c>
       <c r="C14">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B15">
         <v>6</v>
       </c>
       <c r="C15">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="B16">
         <v>6</v>
       </c>
       <c r="C16">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="B17">
         <v>6</v>
       </c>
       <c r="C17">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -21872,491 +20900,491 @@
         <v>6</v>
       </c>
       <c r="C18">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B19">
         <v>6</v>
       </c>
       <c r="C19">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B20">
         <v>6</v>
       </c>
       <c r="C20">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
       <c r="C21">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B22">
         <v>6</v>
       </c>
       <c r="C22">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>124</v>
       </c>
       <c r="B23">
         <v>6</v>
       </c>
       <c r="C23">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="B24">
         <v>6</v>
       </c>
       <c r="C24">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="B25">
         <v>6</v>
       </c>
       <c r="C25">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="B26">
         <v>6</v>
       </c>
       <c r="C26">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="B27">
         <v>6</v>
       </c>
       <c r="C27">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="B28">
         <v>6</v>
       </c>
       <c r="C28">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B29">
         <v>6</v>
       </c>
       <c r="C29">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="B30">
         <v>6</v>
       </c>
       <c r="C30">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="B31">
         <v>6</v>
       </c>
       <c r="C31">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>101</v>
       </c>
       <c r="B32">
         <v>6</v>
       </c>
       <c r="C32">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="B33">
         <v>6</v>
       </c>
       <c r="C33">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="B34">
         <v>6</v>
       </c>
       <c r="C34">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="B35">
         <v>6</v>
       </c>
       <c r="C35">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B36">
         <v>6</v>
       </c>
       <c r="C36">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="B37">
         <v>6</v>
       </c>
       <c r="C37">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="B38">
         <v>6</v>
       </c>
       <c r="C38">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="B39">
         <v>6</v>
       </c>
       <c r="C39">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="B40">
         <v>6</v>
       </c>
       <c r="C40">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="B41">
         <v>6</v>
       </c>
       <c r="C41">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="B42">
         <v>6</v>
       </c>
       <c r="C42">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="B43">
         <v>6</v>
       </c>
       <c r="C43">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="B44">
         <v>6</v>
       </c>
       <c r="C44">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="B45">
         <v>6</v>
       </c>
       <c r="C45">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="B46">
         <v>6</v>
       </c>
       <c r="C46">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="B47">
         <v>6</v>
       </c>
       <c r="C47">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="B48">
         <v>6</v>
       </c>
       <c r="C48">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="B49">
         <v>6</v>
       </c>
       <c r="C49">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="B50">
         <v>6</v>
       </c>
       <c r="C50">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="B51">
         <v>6</v>
       </c>
       <c r="C51">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="B52">
         <v>6</v>
       </c>
       <c r="C52">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="B53">
         <v>6</v>
       </c>
       <c r="C53">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="B54">
         <v>6</v>
       </c>
       <c r="C54">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="B55">
         <v>6</v>
       </c>
       <c r="C55">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B56">
         <v>6</v>
       </c>
       <c r="C56">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="B57">
         <v>6</v>
       </c>
       <c r="C57">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B58">
         <v>6</v>
       </c>
       <c r="C58">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>33</v>
+        <v>125</v>
       </c>
       <c r="B59">
         <v>6</v>
       </c>
       <c r="C59">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B60">
         <v>6</v>
       </c>
       <c r="C60">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="B61">
         <v>6</v>
       </c>
       <c r="C61">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B62">
         <v>6</v>
       </c>
       <c r="C62">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -22367,7 +21395,7 @@
         <v>6</v>
       </c>
       <c r="C63">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -22378,7 +21406,7 @@
         <v>6</v>
       </c>
       <c r="C64">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -22389,7 +21417,7 @@
         <v>6</v>
       </c>
       <c r="C65">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -22400,7 +21428,7 @@
         <v>6</v>
       </c>
       <c r="C66">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -22411,7 +21439,7 @@
         <v>6</v>
       </c>
       <c r="C67">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -22422,7 +21450,7 @@
         <v>6</v>
       </c>
       <c r="C68">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -22433,7 +21461,7 @@
         <v>6</v>
       </c>
       <c r="C69">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -22444,7 +21472,7 @@
         <v>6</v>
       </c>
       <c r="C70">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -22455,56 +21483,56 @@
         <v>6</v>
       </c>
       <c r="C71">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B72">
         <v>5</v>
       </c>
       <c r="C72">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="B73">
         <v>5</v>
       </c>
       <c r="C73">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B74">
         <v>5</v>
       </c>
       <c r="C74">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B75">
         <v>5</v>
       </c>
       <c r="C75">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="B76">
         <v>5</v>
@@ -22515,7 +21543,7 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="B77">
         <v>5</v>
@@ -22526,51 +21554,51 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="B78">
         <v>5</v>
       </c>
       <c r="C78">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="B79">
         <v>5</v>
       </c>
       <c r="C79">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="B80">
         <v>5</v>
       </c>
       <c r="C80">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="B81">
         <v>5</v>
       </c>
       <c r="C81">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="B82">
         <v>5</v>
@@ -22587,7 +21615,7 @@
         <v>5</v>
       </c>
       <c r="C83">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -22598,7 +21626,7 @@
         <v>5</v>
       </c>
       <c r="C84">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -22609,7 +21637,7 @@
         <v>5</v>
       </c>
       <c r="C85">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -22620,56 +21648,56 @@
         <v>5</v>
       </c>
       <c r="C86">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="B87">
         <v>5</v>
       </c>
       <c r="C87">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B88">
         <v>5</v>
       </c>
       <c r="C88">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B89">
         <v>5</v>
       </c>
       <c r="C89">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="B90">
         <v>5</v>
       </c>
       <c r="C90">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="B91">
         <v>5</v>
@@ -22680,7 +21708,7 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>68</v>
+        <v>117</v>
       </c>
       <c r="B92">
         <v>5</v>
@@ -22691,51 +21719,51 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="B93">
         <v>5</v>
       </c>
       <c r="C93">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>103</v>
+        <v>37</v>
       </c>
       <c r="B94">
         <v>5</v>
       </c>
       <c r="C94">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="B95">
         <v>5</v>
       </c>
       <c r="C95">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="B96">
         <v>5</v>
       </c>
       <c r="C96">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="B97">
         <v>5</v>
@@ -22746,7 +21774,7 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="B98">
         <v>5</v>
@@ -22757,7 +21785,7 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="B99">
         <v>5</v>
@@ -22768,29 +21796,29 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="B100">
         <v>5</v>
       </c>
       <c r="C100">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>118</v>
+        <v>55</v>
       </c>
       <c r="B101">
         <v>5</v>
       </c>
       <c r="C101">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="B102">
         <v>5</v>
@@ -22807,12 +21835,12 @@
         <v>5</v>
       </c>
       <c r="C103">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="B104">
         <v>5</v>
@@ -22823,35 +21851,35 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="B105">
         <v>5</v>
       </c>
       <c r="C105">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="B106">
         <v>5</v>
       </c>
       <c r="C106">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="B107">
         <v>5</v>
       </c>
       <c r="C107">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -22873,34 +21901,34 @@
         <v>4</v>
       </c>
       <c r="C109">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B110">
         <v>4</v>
       </c>
       <c r="C110">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B111">
         <v>4</v>
       </c>
       <c r="C111">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="B112">
         <v>4</v>
@@ -22911,24 +21939,24 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="B113">
         <v>4</v>
       </c>
       <c r="C113">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B114">
         <v>4</v>
       </c>
       <c r="C114">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:3">

--- a/02-Execucao/03-Execucao_Procedimentos/02-Resultados_Auditoria/tabelas_consolidadas_auditoria.xlsx
+++ b/02-Execucao/03-Execucao_Procedimentos/02-Resultados_Auditoria/tabelas_consolidadas_auditoria.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4718" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4774" uniqueCount="310">
   <si>
     <t>Nome</t>
   </si>
@@ -796,6 +796,9 @@
   </si>
   <si>
     <t>[Determinação] assegure que as contratações de TIC sejam compatíveis com os instrumentos de planejamento de TIC e, quando elaborado, com o Plano de Contratações Anual, promovendo os ajustes ou justificativas cabíveis nos casos excepcionais</t>
+  </si>
+  <si>
+    <t>[Determinação] defina formalmente as atribuições da área de TIC, atentando-se, minimamente, em abranger as atividades de planejamento, coordenação, gestão e controle da TIC</t>
   </si>
   <si>
     <t>[Determinação] estabeleça e execute rotina periódica de acompanhamento da execução do plano de TIC, promovendo sua revisão periódica e os ajustes ou atualizações necessários, com registro das principais decisões e reprogramações</t>
@@ -6250,10 +6253,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z114"/>
+  <dimension ref="A1:AA114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -6332,59 +6335,62 @@
       <c r="Z1" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="2" spans="1:26">
+      <c r="AA1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="L2" t="s">
-        <v>256</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="D2" t="s">
+        <v>256</v>
+      </c>
+      <c r="M2" t="s">
         <v>256</v>
       </c>
       <c r="P2" t="s">
         <v>256</v>
       </c>
-      <c r="R2" t="s">
-        <v>256</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="Q2" t="s">
+        <v>256</v>
+      </c>
+      <c r="S2" t="s">
         <v>256</v>
       </c>
       <c r="U2" t="s">
         <v>256</v>
       </c>
-      <c r="W2" t="s">
+      <c r="V2" t="s">
         <v>256</v>
       </c>
       <c r="X2" t="s">
         <v>256</v>
       </c>
-      <c r="Z2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26">
+      <c r="Y2" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27">
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="H3" t="s">
-        <v>256</v>
-      </c>
       <c r="I3" t="s">
         <v>256</v>
       </c>
-      <c r="L3" t="s">
-        <v>256</v>
-      </c>
-      <c r="T3" t="s">
+      <c r="J3" t="s">
+        <v>256</v>
+      </c>
+      <c r="M3" t="s">
         <v>256</v>
       </c>
       <c r="U3" t="s">
         <v>256</v>
       </c>
-      <c r="W3" t="s">
+      <c r="V3" t="s">
         <v>256</v>
       </c>
       <c r="X3" t="s">
@@ -6393,27 +6399,30 @@
       <c r="Y3" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="4" spans="1:26">
+      <c r="Z3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27">
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D4" t="s">
         <v>256</v>
       </c>
       <c r="F4" t="s">
         <v>256</v>
       </c>
-      <c r="L4" t="s">
-        <v>256</v>
-      </c>
-      <c r="O4" t="s">
+      <c r="G4" t="s">
+        <v>256</v>
+      </c>
+      <c r="M4" t="s">
         <v>256</v>
       </c>
       <c r="P4" t="s">
         <v>256</v>
       </c>
-      <c r="R4" t="s">
+      <c r="Q4" t="s">
         <v>256</v>
       </c>
       <c r="S4" t="s">
@@ -6425,7 +6434,7 @@
       <c r="U4" t="s">
         <v>256</v>
       </c>
-      <c r="W4" t="s">
+      <c r="V4" t="s">
         <v>256</v>
       </c>
       <c r="X4" t="s">
@@ -6437,24 +6446,27 @@
       <c r="Z4" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="5" spans="1:26">
+      <c r="AA4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="C5" t="s">
         <v>256</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D5" t="s">
         <v>256</v>
       </c>
       <c r="F5" t="s">
         <v>256</v>
       </c>
-      <c r="L5" t="s">
-        <v>256</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="G5" t="s">
+        <v>256</v>
+      </c>
+      <c r="M5" t="s">
         <v>256</v>
       </c>
       <c r="P5" t="s">
@@ -6475,7 +6487,7 @@
       <c r="U5" t="s">
         <v>256</v>
       </c>
-      <c r="W5" t="s">
+      <c r="V5" t="s">
         <v>256</v>
       </c>
       <c r="X5" t="s">
@@ -6487,24 +6499,27 @@
       <c r="Z5" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="6" spans="1:26">
+      <c r="AA5" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="C6" t="s">
         <v>256</v>
       </c>
-      <c r="E6" t="s">
+      <c r="D6" t="s">
         <v>256</v>
       </c>
       <c r="F6" t="s">
         <v>256</v>
       </c>
-      <c r="L6" t="s">
-        <v>256</v>
-      </c>
-      <c r="O6" t="s">
+      <c r="G6" t="s">
+        <v>256</v>
+      </c>
+      <c r="M6" t="s">
         <v>256</v>
       </c>
       <c r="P6" t="s">
@@ -6525,7 +6540,7 @@
       <c r="U6" t="s">
         <v>256</v>
       </c>
-      <c r="W6" t="s">
+      <c r="V6" t="s">
         <v>256</v>
       </c>
       <c r="X6" t="s">
@@ -6537,24 +6552,24 @@
       <c r="Z6" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="7" spans="1:26">
+      <c r="AA6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>256</v>
       </c>
-      <c r="F7" t="s">
-        <v>256</v>
-      </c>
-      <c r="L7" t="s">
-        <v>256</v>
-      </c>
-      <c r="P7" t="s">
-        <v>256</v>
-      </c>
-      <c r="R7" t="s">
+      <c r="G7" t="s">
+        <v>256</v>
+      </c>
+      <c r="M7" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q7" t="s">
         <v>256</v>
       </c>
       <c r="S7" t="s">
@@ -6566,7 +6581,7 @@
       <c r="U7" t="s">
         <v>256</v>
       </c>
-      <c r="W7" t="s">
+      <c r="V7" t="s">
         <v>256</v>
       </c>
       <c r="X7" t="s">
@@ -6578,33 +6593,33 @@
       <c r="Z7" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="8" spans="1:26">
+      <c r="AA7" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="C8" t="s">
         <v>256</v>
       </c>
-      <c r="E8" t="s">
-        <v>256</v>
-      </c>
       <c r="F8" t="s">
         <v>256</v>
       </c>
-      <c r="N8" t="s">
-        <v>256</v>
-      </c>
-      <c r="P8" t="s">
+      <c r="G8" t="s">
+        <v>256</v>
+      </c>
+      <c r="O8" t="s">
         <v>256</v>
       </c>
       <c r="Q8" t="s">
         <v>256</v>
       </c>
-      <c r="U8" t="s">
-        <v>256</v>
-      </c>
-      <c r="W8" t="s">
+      <c r="R8" t="s">
+        <v>256</v>
+      </c>
+      <c r="V8" t="s">
         <v>256</v>
       </c>
       <c r="X8" t="s">
@@ -6616,18 +6631,21 @@
       <c r="Z8" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="9" spans="1:26">
+      <c r="AA8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27">
       <c r="A9" t="s">
         <v>15</v>
       </c>
-      <c r="E9" t="s">
+      <c r="D9" t="s">
         <v>256</v>
       </c>
       <c r="F9" t="s">
         <v>256</v>
       </c>
-      <c r="N9" t="s">
+      <c r="G9" t="s">
         <v>256</v>
       </c>
       <c r="O9" t="s">
@@ -6651,7 +6669,7 @@
       <c r="U9" t="s">
         <v>256</v>
       </c>
-      <c r="W9" t="s">
+      <c r="V9" t="s">
         <v>256</v>
       </c>
       <c r="X9" t="s">
@@ -6663,24 +6681,27 @@
       <c r="Z9" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="10" spans="1:26">
+      <c r="AA9" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27">
       <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="E10" t="s">
-        <v>256</v>
-      </c>
-      <c r="L10" t="s">
-        <v>256</v>
-      </c>
-      <c r="O10" t="s">
+      <c r="D10" t="s">
+        <v>256</v>
+      </c>
+      <c r="F10" t="s">
+        <v>256</v>
+      </c>
+      <c r="M10" t="s">
         <v>256</v>
       </c>
       <c r="P10" t="s">
         <v>256</v>
       </c>
-      <c r="S10" t="s">
+      <c r="Q10" t="s">
         <v>256</v>
       </c>
       <c r="T10" t="s">
@@ -6689,56 +6710,56 @@
       <c r="U10" t="s">
         <v>256</v>
       </c>
-      <c r="W10" t="s">
+      <c r="V10" t="s">
         <v>256</v>
       </c>
       <c r="X10" t="s">
         <v>256</v>
       </c>
-      <c r="Z10" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26">
+      <c r="Y10" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27">
       <c r="A11" t="s">
         <v>17</v>
       </c>
-      <c r="L11" t="s">
-        <v>256</v>
-      </c>
-      <c r="P11" t="s">
-        <v>256</v>
-      </c>
-      <c r="R11" t="s">
+      <c r="M11" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q11" t="s">
         <v>256</v>
       </c>
       <c r="S11" t="s">
         <v>256</v>
       </c>
-      <c r="U11" t="s">
-        <v>256</v>
-      </c>
-      <c r="W11" t="s">
-        <v>256</v>
-      </c>
-      <c r="Y11" t="s">
+      <c r="T11" t="s">
+        <v>256</v>
+      </c>
+      <c r="V11" t="s">
+        <v>256</v>
+      </c>
+      <c r="X11" t="s">
         <v>256</v>
       </c>
       <c r="Z11" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="12" spans="1:26">
+      <c r="AA11" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27">
       <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="D12" t="s">
-        <v>256</v>
-      </c>
-      <c r="F12" t="s">
-        <v>256</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="E12" t="s">
+        <v>256</v>
+      </c>
+      <c r="G12" t="s">
         <v>256</v>
       </c>
       <c r="I12" t="s">
@@ -6747,13 +6768,13 @@
       <c r="J12" t="s">
         <v>256</v>
       </c>
-      <c r="L12" t="s">
-        <v>256</v>
-      </c>
-      <c r="P12" t="s">
-        <v>256</v>
-      </c>
-      <c r="R12" t="s">
+      <c r="K12" t="s">
+        <v>256</v>
+      </c>
+      <c r="M12" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q12" t="s">
         <v>256</v>
       </c>
       <c r="S12" t="s">
@@ -6765,7 +6786,7 @@
       <c r="U12" t="s">
         <v>256</v>
       </c>
-      <c r="W12" t="s">
+      <c r="V12" t="s">
         <v>256</v>
       </c>
       <c r="X12" t="s">
@@ -6777,8 +6798,11 @@
       <c r="Z12" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="13" spans="1:26">
+      <c r="AA12" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -6788,10 +6812,10 @@
       <c r="E13" t="s">
         <v>256</v>
       </c>
-      <c r="L13" t="s">
-        <v>256</v>
-      </c>
-      <c r="N13" t="s">
+      <c r="F13" t="s">
+        <v>256</v>
+      </c>
+      <c r="M13" t="s">
         <v>256</v>
       </c>
       <c r="O13" t="s">
@@ -6800,42 +6824,42 @@
       <c r="P13" t="s">
         <v>256</v>
       </c>
-      <c r="R13" t="s">
+      <c r="Q13" t="s">
         <v>256</v>
       </c>
       <c r="S13" t="s">
         <v>256</v>
       </c>
-      <c r="U13" t="s">
-        <v>256</v>
-      </c>
-      <c r="W13" t="s">
+      <c r="T13" t="s">
+        <v>256</v>
+      </c>
+      <c r="V13" t="s">
         <v>256</v>
       </c>
       <c r="X13" t="s">
         <v>256</v>
       </c>
-      <c r="Z13" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26">
+      <c r="Y13" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27">
       <c r="A14" t="s">
         <v>20</v>
       </c>
       <c r="B14" t="s">
         <v>256</v>
       </c>
-      <c r="D14" t="s">
-        <v>256</v>
-      </c>
-      <c r="L14" t="s">
-        <v>256</v>
-      </c>
-      <c r="P14" t="s">
-        <v>256</v>
-      </c>
-      <c r="R14" t="s">
+      <c r="E14" t="s">
+        <v>256</v>
+      </c>
+      <c r="M14" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q14" t="s">
         <v>256</v>
       </c>
       <c r="S14" t="s">
@@ -6847,7 +6871,7 @@
       <c r="U14" t="s">
         <v>256</v>
       </c>
-      <c r="W14" t="s">
+      <c r="V14" t="s">
         <v>256</v>
       </c>
       <c r="X14" t="s">
@@ -6859,27 +6883,30 @@
       <c r="Z14" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="15" spans="1:26">
+      <c r="AA14" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27">
       <c r="A15" t="s">
         <v>21</v>
       </c>
-      <c r="E15" t="s">
+      <c r="D15" t="s">
         <v>256</v>
       </c>
       <c r="F15" t="s">
         <v>256</v>
       </c>
-      <c r="I15" t="s">
+      <c r="G15" t="s">
         <v>256</v>
       </c>
       <c r="J15" t="s">
         <v>256</v>
       </c>
-      <c r="L15" t="s">
-        <v>256</v>
-      </c>
-      <c r="O15" t="s">
+      <c r="K15" t="s">
+        <v>256</v>
+      </c>
+      <c r="M15" t="s">
         <v>256</v>
       </c>
       <c r="P15" t="s">
@@ -6900,7 +6927,7 @@
       <c r="U15" t="s">
         <v>256</v>
       </c>
-      <c r="W15" t="s">
+      <c r="V15" t="s">
         <v>256</v>
       </c>
       <c r="X15" t="s">
@@ -6912,8 +6939,11 @@
       <c r="Z15" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="16" spans="1:26">
+      <c r="AA15" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -6923,35 +6953,35 @@
       <c r="C16" t="s">
         <v>256</v>
       </c>
-      <c r="E16" t="s">
-        <v>256</v>
-      </c>
       <c r="F16" t="s">
         <v>256</v>
       </c>
-      <c r="P16" t="s">
-        <v>256</v>
-      </c>
-      <c r="R16" t="s">
-        <v>256</v>
-      </c>
-      <c r="T16" t="s">
+      <c r="G16" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>256</v>
+      </c>
+      <c r="S16" t="s">
         <v>256</v>
       </c>
       <c r="U16" t="s">
         <v>256</v>
       </c>
-      <c r="W16" t="s">
+      <c r="V16" t="s">
         <v>256</v>
       </c>
       <c r="X16" t="s">
         <v>256</v>
       </c>
-      <c r="Z16" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26">
+      <c r="Y16" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -6964,16 +6994,16 @@
       <c r="F17" t="s">
         <v>256</v>
       </c>
-      <c r="L17" t="s">
-        <v>256</v>
-      </c>
-      <c r="O17" t="s">
+      <c r="G17" t="s">
+        <v>256</v>
+      </c>
+      <c r="M17" t="s">
         <v>256</v>
       </c>
       <c r="P17" t="s">
         <v>256</v>
       </c>
-      <c r="R17" t="s">
+      <c r="Q17" t="s">
         <v>256</v>
       </c>
       <c r="S17" t="s">
@@ -6985,7 +7015,7 @@
       <c r="U17" t="s">
         <v>256</v>
       </c>
-      <c r="W17" t="s">
+      <c r="V17" t="s">
         <v>256</v>
       </c>
       <c r="X17" t="s">
@@ -6997,27 +7027,27 @@
       <c r="Z17" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="18" spans="1:26">
+      <c r="AA17" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27">
       <c r="A18" t="s">
         <v>24</v>
       </c>
       <c r="B18" t="s">
         <v>256</v>
       </c>
-      <c r="F18" t="s">
-        <v>256</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="G18" t="s">
         <v>256</v>
       </c>
       <c r="J18" t="s">
         <v>256</v>
       </c>
-      <c r="L18" t="s">
-        <v>256</v>
-      </c>
-      <c r="P18" t="s">
+      <c r="K18" t="s">
+        <v>256</v>
+      </c>
+      <c r="M18" t="s">
         <v>256</v>
       </c>
       <c r="Q18" t="s">
@@ -7035,65 +7065,65 @@
       <c r="U18" t="s">
         <v>256</v>
       </c>
-      <c r="W18" t="s">
+      <c r="V18" t="s">
         <v>256</v>
       </c>
       <c r="X18" t="s">
         <v>256</v>
       </c>
-      <c r="Z18" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26">
+      <c r="Y18" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27">
       <c r="A19" t="s">
         <v>25</v>
       </c>
-      <c r="D19" t="s">
-        <v>256</v>
-      </c>
       <c r="E19" t="s">
         <v>256</v>
       </c>
       <c r="F19" t="s">
         <v>256</v>
       </c>
-      <c r="L19" t="s">
-        <v>256</v>
-      </c>
-      <c r="N19" t="s">
-        <v>256</v>
-      </c>
-      <c r="P19" t="s">
-        <v>256</v>
-      </c>
-      <c r="T19" t="s">
+      <c r="G19" t="s">
+        <v>256</v>
+      </c>
+      <c r="M19" t="s">
+        <v>256</v>
+      </c>
+      <c r="O19" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q19" t="s">
         <v>256</v>
       </c>
       <c r="U19" t="s">
         <v>256</v>
       </c>
-      <c r="W19" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26">
+      <c r="V19" t="s">
+        <v>256</v>
+      </c>
+      <c r="X19" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27">
       <c r="A20" t="s">
         <v>26</v>
       </c>
-      <c r="E20" t="s">
-        <v>256</v>
-      </c>
       <c r="F20" t="s">
         <v>256</v>
       </c>
-      <c r="L20" t="s">
-        <v>256</v>
-      </c>
-      <c r="P20" t="s">
-        <v>256</v>
-      </c>
-      <c r="S20" t="s">
+      <c r="G20" t="s">
+        <v>256</v>
+      </c>
+      <c r="M20" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q20" t="s">
         <v>256</v>
       </c>
       <c r="T20" t="s">
@@ -7102,7 +7132,7 @@
       <c r="U20" t="s">
         <v>256</v>
       </c>
-      <c r="W20" t="s">
+      <c r="V20" t="s">
         <v>256</v>
       </c>
       <c r="X20" t="s">
@@ -7114,8 +7144,11 @@
       <c r="Z20" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="21" spans="1:26">
+      <c r="AA20" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -7128,16 +7161,16 @@
       <c r="F21" t="s">
         <v>256</v>
       </c>
-      <c r="H21" t="s">
-        <v>256</v>
-      </c>
-      <c r="J21" t="s">
-        <v>256</v>
-      </c>
-      <c r="L21" t="s">
-        <v>256</v>
-      </c>
-      <c r="N21" t="s">
+      <c r="G21" t="s">
+        <v>256</v>
+      </c>
+      <c r="I21" t="s">
+        <v>256</v>
+      </c>
+      <c r="K21" t="s">
+        <v>256</v>
+      </c>
+      <c r="M21" t="s">
         <v>256</v>
       </c>
       <c r="O21" t="s">
@@ -7161,7 +7194,7 @@
       <c r="U21" t="s">
         <v>256</v>
       </c>
-      <c r="W21" t="s">
+      <c r="V21" t="s">
         <v>256</v>
       </c>
       <c r="X21" t="s">
@@ -7173,21 +7206,24 @@
       <c r="Z21" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="22" spans="1:26">
+      <c r="AA21" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27">
       <c r="A22" t="s">
         <v>29</v>
       </c>
-      <c r="E22" t="s">
-        <v>256</v>
-      </c>
-      <c r="J22" t="s">
-        <v>256</v>
-      </c>
-      <c r="L22" t="s">
-        <v>256</v>
-      </c>
-      <c r="O22" t="s">
+      <c r="D22" t="s">
+        <v>256</v>
+      </c>
+      <c r="F22" t="s">
+        <v>256</v>
+      </c>
+      <c r="K22" t="s">
+        <v>256</v>
+      </c>
+      <c r="M22" t="s">
         <v>256</v>
       </c>
       <c r="P22" t="s">
@@ -7208,7 +7244,7 @@
       <c r="U22" t="s">
         <v>256</v>
       </c>
-      <c r="W22" t="s">
+      <c r="V22" t="s">
         <v>256</v>
       </c>
       <c r="X22" t="s">
@@ -7220,21 +7256,21 @@
       <c r="Z22" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="23" spans="1:26">
+      <c r="AA22" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27">
       <c r="A23" t="s">
         <v>30</v>
       </c>
-      <c r="E23" t="s">
-        <v>256</v>
-      </c>
       <c r="F23" t="s">
         <v>256</v>
       </c>
-      <c r="L23" t="s">
-        <v>256</v>
-      </c>
-      <c r="P23" t="s">
+      <c r="G23" t="s">
+        <v>256</v>
+      </c>
+      <c r="M23" t="s">
         <v>256</v>
       </c>
       <c r="Q23" t="s">
@@ -7267,8 +7303,11 @@
       <c r="Z23" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="24" spans="1:26">
+      <c r="AA23" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -7281,16 +7320,16 @@
       <c r="F24" t="s">
         <v>256</v>
       </c>
-      <c r="H24" t="s">
-        <v>256</v>
-      </c>
-      <c r="J24" t="s">
-        <v>256</v>
-      </c>
-      <c r="L24" t="s">
-        <v>256</v>
-      </c>
-      <c r="N24" t="s">
+      <c r="G24" t="s">
+        <v>256</v>
+      </c>
+      <c r="I24" t="s">
+        <v>256</v>
+      </c>
+      <c r="K24" t="s">
+        <v>256</v>
+      </c>
+      <c r="M24" t="s">
         <v>256</v>
       </c>
       <c r="O24" t="s">
@@ -7299,7 +7338,7 @@
       <c r="P24" t="s">
         <v>256</v>
       </c>
-      <c r="S24" t="s">
+      <c r="Q24" t="s">
         <v>256</v>
       </c>
       <c r="T24" t="s">
@@ -7308,7 +7347,7 @@
       <c r="U24" t="s">
         <v>256</v>
       </c>
-      <c r="W24" t="s">
+      <c r="V24" t="s">
         <v>256</v>
       </c>
       <c r="X24" t="s">
@@ -7320,21 +7359,24 @@
       <c r="Z24" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="25" spans="1:26">
+      <c r="AA24" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27">
       <c r="A25" t="s">
         <v>32</v>
       </c>
-      <c r="E25" t="s">
+      <c r="D25" t="s">
         <v>256</v>
       </c>
       <c r="F25" t="s">
         <v>256</v>
       </c>
-      <c r="L25" t="s">
-        <v>256</v>
-      </c>
-      <c r="O25" t="s">
+      <c r="G25" t="s">
+        <v>256</v>
+      </c>
+      <c r="M25" t="s">
         <v>256</v>
       </c>
       <c r="P25" t="s">
@@ -7355,7 +7397,7 @@
       <c r="U25" t="s">
         <v>256</v>
       </c>
-      <c r="W25" t="s">
+      <c r="V25" t="s">
         <v>256</v>
       </c>
       <c r="X25" t="s">
@@ -7367,8 +7409,11 @@
       <c r="Z25" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="26" spans="1:26">
+      <c r="AA25" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -7381,16 +7426,16 @@
       <c r="F26" t="s">
         <v>256</v>
       </c>
-      <c r="H26" t="s">
-        <v>256</v>
-      </c>
-      <c r="O26" t="s">
+      <c r="G26" t="s">
+        <v>256</v>
+      </c>
+      <c r="I26" t="s">
         <v>256</v>
       </c>
       <c r="P26" t="s">
         <v>256</v>
       </c>
-      <c r="R26" t="s">
+      <c r="Q26" t="s">
         <v>256</v>
       </c>
       <c r="S26" t="s">
@@ -7402,55 +7447,58 @@
       <c r="U26" t="s">
         <v>256</v>
       </c>
-      <c r="W26" t="s">
+      <c r="V26" t="s">
         <v>256</v>
       </c>
       <c r="X26" t="s">
         <v>256</v>
       </c>
-      <c r="Z26" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="27" spans="1:26">
+      <c r="Y26" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27">
       <c r="A27" t="s">
         <v>34</v>
       </c>
       <c r="B27" t="s">
         <v>256</v>
       </c>
-      <c r="F27" t="s">
-        <v>256</v>
-      </c>
-      <c r="I27" t="s">
-        <v>256</v>
-      </c>
-      <c r="L27" t="s">
-        <v>256</v>
-      </c>
-      <c r="N27" t="s">
-        <v>256</v>
-      </c>
-      <c r="P27" t="s">
-        <v>256</v>
-      </c>
-      <c r="T27" t="s">
+      <c r="G27" t="s">
+        <v>256</v>
+      </c>
+      <c r="J27" t="s">
+        <v>256</v>
+      </c>
+      <c r="M27" t="s">
+        <v>256</v>
+      </c>
+      <c r="O27" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q27" t="s">
         <v>256</v>
       </c>
       <c r="U27" t="s">
         <v>256</v>
       </c>
-      <c r="W27" t="s">
-        <v>256</v>
-      </c>
-      <c r="Y27" t="s">
+      <c r="V27" t="s">
+        <v>256</v>
+      </c>
+      <c r="X27" t="s">
         <v>256</v>
       </c>
       <c r="Z27" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="28" spans="1:26">
+      <c r="AA27" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -7460,16 +7508,16 @@
       <c r="D28" t="s">
         <v>256</v>
       </c>
-      <c r="F28" t="s">
-        <v>256</v>
-      </c>
-      <c r="I28" t="s">
-        <v>256</v>
-      </c>
-      <c r="L28" t="s">
-        <v>256</v>
-      </c>
-      <c r="N28" t="s">
+      <c r="E28" t="s">
+        <v>256</v>
+      </c>
+      <c r="G28" t="s">
+        <v>256</v>
+      </c>
+      <c r="J28" t="s">
+        <v>256</v>
+      </c>
+      <c r="M28" t="s">
         <v>256</v>
       </c>
       <c r="O28" t="s">
@@ -7478,7 +7526,7 @@
       <c r="P28" t="s">
         <v>256</v>
       </c>
-      <c r="R28" t="s">
+      <c r="Q28" t="s">
         <v>256</v>
       </c>
       <c r="S28" t="s">
@@ -7490,7 +7538,7 @@
       <c r="U28" t="s">
         <v>256</v>
       </c>
-      <c r="W28" t="s">
+      <c r="V28" t="s">
         <v>256</v>
       </c>
       <c r="X28" t="s">
@@ -7502,21 +7550,21 @@
       <c r="Z28" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="29" spans="1:26">
+      <c r="AA28" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27">
       <c r="A29" t="s">
         <v>36</v>
       </c>
-      <c r="E29" t="s">
-        <v>256</v>
-      </c>
       <c r="F29" t="s">
         <v>256</v>
       </c>
-      <c r="L29" t="s">
-        <v>256</v>
-      </c>
-      <c r="P29" t="s">
+      <c r="G29" t="s">
+        <v>256</v>
+      </c>
+      <c r="M29" t="s">
         <v>256</v>
       </c>
       <c r="Q29" t="s">
@@ -7549,30 +7597,30 @@
       <c r="Z29" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="30" spans="1:26">
+      <c r="AA29" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27">
       <c r="A30" t="s">
         <v>37</v>
       </c>
-      <c r="E30" t="s">
-        <v>256</v>
-      </c>
       <c r="F30" t="s">
         <v>256</v>
       </c>
-      <c r="P30" t="s">
-        <v>256</v>
-      </c>
-      <c r="R30" t="s">
-        <v>256</v>
-      </c>
-      <c r="T30" t="s">
+      <c r="G30" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>256</v>
+      </c>
+      <c r="S30" t="s">
         <v>256</v>
       </c>
       <c r="U30" t="s">
         <v>256</v>
       </c>
-      <c r="W30" t="s">
+      <c r="V30" t="s">
         <v>256</v>
       </c>
       <c r="X30" t="s">
@@ -7581,40 +7629,46 @@
       <c r="Y30" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="31" spans="1:26">
+      <c r="Z30" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27">
       <c r="A31" t="s">
         <v>38</v>
       </c>
-      <c r="E31" t="s">
-        <v>256</v>
-      </c>
-      <c r="L31" t="s">
-        <v>256</v>
-      </c>
-      <c r="O31" t="s">
+      <c r="D31" t="s">
+        <v>256</v>
+      </c>
+      <c r="F31" t="s">
+        <v>256</v>
+      </c>
+      <c r="M31" t="s">
         <v>256</v>
       </c>
       <c r="P31" t="s">
         <v>256</v>
       </c>
-      <c r="R31" t="s">
+      <c r="Q31" t="s">
         <v>256</v>
       </c>
       <c r="S31" t="s">
         <v>256</v>
       </c>
-      <c r="U31" t="s">
-        <v>256</v>
-      </c>
-      <c r="W31" t="s">
-        <v>256</v>
-      </c>
-      <c r="Z31" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="32" spans="1:26">
+      <c r="T31" t="s">
+        <v>256</v>
+      </c>
+      <c r="V31" t="s">
+        <v>256</v>
+      </c>
+      <c r="X31" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -7627,19 +7681,19 @@
       <c r="F32" t="s">
         <v>256</v>
       </c>
-      <c r="J32" t="s">
-        <v>256</v>
-      </c>
-      <c r="L32" t="s">
-        <v>256</v>
-      </c>
-      <c r="O32" t="s">
+      <c r="G32" t="s">
+        <v>256</v>
+      </c>
+      <c r="K32" t="s">
+        <v>256</v>
+      </c>
+      <c r="M32" t="s">
         <v>256</v>
       </c>
       <c r="P32" t="s">
         <v>256</v>
       </c>
-      <c r="R32" t="s">
+      <c r="Q32" t="s">
         <v>256</v>
       </c>
       <c r="S32" t="s">
@@ -7651,7 +7705,7 @@
       <c r="U32" t="s">
         <v>256</v>
       </c>
-      <c r="W32" t="s">
+      <c r="V32" t="s">
         <v>256</v>
       </c>
       <c r="X32" t="s">
@@ -7663,36 +7717,39 @@
       <c r="Z32" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="33" spans="1:26">
+      <c r="AA32" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27">
       <c r="A33" t="s">
         <v>40</v>
       </c>
       <c r="B33" t="s">
         <v>256</v>
       </c>
-      <c r="F33" t="s">
-        <v>256</v>
-      </c>
-      <c r="L33" t="s">
-        <v>256</v>
-      </c>
-      <c r="O33" t="s">
+      <c r="D33" t="s">
+        <v>256</v>
+      </c>
+      <c r="G33" t="s">
+        <v>256</v>
+      </c>
+      <c r="M33" t="s">
         <v>256</v>
       </c>
       <c r="P33" t="s">
         <v>256</v>
       </c>
-      <c r="R33" t="s">
+      <c r="Q33" t="s">
         <v>256</v>
       </c>
       <c r="S33" t="s">
         <v>256</v>
       </c>
-      <c r="U33" t="s">
-        <v>256</v>
-      </c>
-      <c r="W33" t="s">
+      <c r="T33" t="s">
+        <v>256</v>
+      </c>
+      <c r="V33" t="s">
         <v>256</v>
       </c>
       <c r="X33" t="s">
@@ -7704,27 +7761,27 @@
       <c r="Z33" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="34" spans="1:26">
+      <c r="AA33" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27">
       <c r="A34" t="s">
         <v>41</v>
       </c>
       <c r="C34" t="s">
         <v>256</v>
       </c>
-      <c r="E34" t="s">
-        <v>256</v>
-      </c>
       <c r="F34" t="s">
         <v>256</v>
       </c>
-      <c r="L34" t="s">
-        <v>256</v>
-      </c>
-      <c r="P34" t="s">
-        <v>256</v>
-      </c>
-      <c r="R34" t="s">
+      <c r="G34" t="s">
+        <v>256</v>
+      </c>
+      <c r="M34" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q34" t="s">
         <v>256</v>
       </c>
       <c r="S34" t="s">
@@ -7736,7 +7793,7 @@
       <c r="U34" t="s">
         <v>256</v>
       </c>
-      <c r="W34" t="s">
+      <c r="V34" t="s">
         <v>256</v>
       </c>
       <c r="X34" t="s">
@@ -7748,24 +7805,24 @@
       <c r="Z34" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="35" spans="1:26">
+      <c r="AA34" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27">
       <c r="A35" t="s">
         <v>42</v>
       </c>
       <c r="B35" t="s">
         <v>256</v>
       </c>
-      <c r="P35" t="s">
-        <v>256</v>
-      </c>
-      <c r="R35" t="s">
-        <v>256</v>
-      </c>
-      <c r="T35" t="s">
-        <v>256</v>
-      </c>
-      <c r="W35" t="s">
+      <c r="Q35" t="s">
+        <v>256</v>
+      </c>
+      <c r="S35" t="s">
+        <v>256</v>
+      </c>
+      <c r="U35" t="s">
         <v>256</v>
       </c>
       <c r="X35" t="s">
@@ -7777,24 +7834,24 @@
       <c r="Z35" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="36" spans="1:26">
+      <c r="AA35" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27">
       <c r="A36" t="s">
         <v>43</v>
       </c>
-      <c r="E36" t="s">
-        <v>256</v>
-      </c>
       <c r="F36" t="s">
         <v>256</v>
       </c>
-      <c r="J36" t="s">
-        <v>256</v>
-      </c>
-      <c r="L36" t="s">
-        <v>256</v>
-      </c>
-      <c r="P36" t="s">
+      <c r="G36" t="s">
+        <v>256</v>
+      </c>
+      <c r="K36" t="s">
+        <v>256</v>
+      </c>
+      <c r="M36" t="s">
         <v>256</v>
       </c>
       <c r="Q36" t="s">
@@ -7803,13 +7860,13 @@
       <c r="R36" t="s">
         <v>256</v>
       </c>
-      <c r="T36" t="s">
+      <c r="S36" t="s">
         <v>256</v>
       </c>
       <c r="U36" t="s">
         <v>256</v>
       </c>
-      <c r="W36" t="s">
+      <c r="V36" t="s">
         <v>256</v>
       </c>
       <c r="X36" t="s">
@@ -7821,8 +7878,11 @@
       <c r="Z36" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="37" spans="1:26">
+      <c r="AA36" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -7832,13 +7892,13 @@
       <c r="E37" t="s">
         <v>256</v>
       </c>
-      <c r="J37" t="s">
-        <v>256</v>
-      </c>
-      <c r="L37" t="s">
-        <v>256</v>
-      </c>
-      <c r="O37" t="s">
+      <c r="F37" t="s">
+        <v>256</v>
+      </c>
+      <c r="K37" t="s">
+        <v>256</v>
+      </c>
+      <c r="M37" t="s">
         <v>256</v>
       </c>
       <c r="P37" t="s">
@@ -7850,7 +7910,7 @@
       <c r="R37" t="s">
         <v>256</v>
       </c>
-      <c r="W37" t="s">
+      <c r="S37" t="s">
         <v>256</v>
       </c>
       <c r="X37" t="s">
@@ -7862,24 +7922,24 @@
       <c r="Z37" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="38" spans="1:26">
+      <c r="AA37" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27">
       <c r="A38" t="s">
         <v>45</v>
       </c>
       <c r="C38" t="s">
         <v>256</v>
       </c>
-      <c r="D38" t="s">
-        <v>256</v>
-      </c>
       <c r="E38" t="s">
         <v>256</v>
       </c>
       <c r="F38" t="s">
         <v>256</v>
       </c>
-      <c r="H38" t="s">
+      <c r="G38" t="s">
         <v>256</v>
       </c>
       <c r="I38" t="s">
@@ -7888,25 +7948,25 @@
       <c r="J38" t="s">
         <v>256</v>
       </c>
-      <c r="L38" t="s">
-        <v>256</v>
-      </c>
-      <c r="N38" t="s">
-        <v>256</v>
-      </c>
-      <c r="P38" t="s">
-        <v>256</v>
-      </c>
-      <c r="R38" t="s">
-        <v>256</v>
-      </c>
-      <c r="T38" t="s">
+      <c r="K38" t="s">
+        <v>256</v>
+      </c>
+      <c r="M38" t="s">
+        <v>256</v>
+      </c>
+      <c r="O38" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>256</v>
+      </c>
+      <c r="S38" t="s">
         <v>256</v>
       </c>
       <c r="U38" t="s">
         <v>256</v>
       </c>
-      <c r="W38" t="s">
+      <c r="V38" t="s">
         <v>256</v>
       </c>
       <c r="X38" t="s">
@@ -7918,8 +7978,11 @@
       <c r="Z38" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="39" spans="1:26">
+      <c r="AA38" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -7929,22 +7992,22 @@
       <c r="D39" t="s">
         <v>256</v>
       </c>
-      <c r="F39" t="s">
-        <v>256</v>
-      </c>
-      <c r="I39" t="s">
+      <c r="E39" t="s">
+        <v>256</v>
+      </c>
+      <c r="G39" t="s">
         <v>256</v>
       </c>
       <c r="J39" t="s">
         <v>256</v>
       </c>
-      <c r="L39" t="s">
+      <c r="K39" t="s">
         <v>256</v>
       </c>
       <c r="M39" t="s">
         <v>256</v>
       </c>
-      <c r="O39" t="s">
+      <c r="N39" t="s">
         <v>256</v>
       </c>
       <c r="P39" t="s">
@@ -7953,7 +8016,7 @@
       <c r="Q39" t="s">
         <v>256</v>
       </c>
-      <c r="S39" t="s">
+      <c r="R39" t="s">
         <v>256</v>
       </c>
       <c r="T39" t="s">
@@ -7962,7 +8025,7 @@
       <c r="U39" t="s">
         <v>256</v>
       </c>
-      <c r="W39" t="s">
+      <c r="V39" t="s">
         <v>256</v>
       </c>
       <c r="X39" t="s">
@@ -7974,32 +8037,32 @@
       <c r="Z39" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="40" spans="1:26">
+      <c r="AA39" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27">
       <c r="A40" t="s">
         <v>47</v>
       </c>
-      <c r="P40" t="s">
-        <v>256</v>
-      </c>
-      <c r="W40" t="s">
-        <v>256</v>
-      </c>
-      <c r="Z40" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="41" spans="1:26">
+      <c r="Q40" t="s">
+        <v>256</v>
+      </c>
+      <c r="X40" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27">
       <c r="A41" t="s">
         <v>48</v>
       </c>
       <c r="B41" t="s">
         <v>256</v>
       </c>
-      <c r="F41" t="s">
-        <v>256</v>
-      </c>
-      <c r="P41" t="s">
+      <c r="G41" t="s">
         <v>256</v>
       </c>
       <c r="Q41" t="s">
@@ -8008,13 +8071,13 @@
       <c r="R41" t="s">
         <v>256</v>
       </c>
-      <c r="T41" t="s">
+      <c r="S41" t="s">
         <v>256</v>
       </c>
       <c r="U41" t="s">
         <v>256</v>
       </c>
-      <c r="W41" t="s">
+      <c r="V41" t="s">
         <v>256</v>
       </c>
       <c r="X41" t="s">
@@ -8026,55 +8089,58 @@
       <c r="Z41" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="42" spans="1:26">
+      <c r="AA41" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27">
       <c r="A42" t="s">
         <v>49</v>
       </c>
-      <c r="L42" t="s">
-        <v>256</v>
-      </c>
-      <c r="U42" t="s">
-        <v>256</v>
-      </c>
-      <c r="W42" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="43" spans="1:26">
+      <c r="M42" t="s">
+        <v>256</v>
+      </c>
+      <c r="V42" t="s">
+        <v>256</v>
+      </c>
+      <c r="X42" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27">
       <c r="A43" t="s">
         <v>51</v>
       </c>
-      <c r="P43" t="s">
-        <v>256</v>
-      </c>
-      <c r="R43" t="s">
-        <v>256</v>
-      </c>
-      <c r="U43" t="s">
-        <v>256</v>
-      </c>
-      <c r="W43" t="s">
-        <v>256</v>
-      </c>
-      <c r="Z43" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="44" spans="1:26">
+      <c r="Q43" t="s">
+        <v>256</v>
+      </c>
+      <c r="S43" t="s">
+        <v>256</v>
+      </c>
+      <c r="V43" t="s">
+        <v>256</v>
+      </c>
+      <c r="X43" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27">
       <c r="A44" t="s">
         <v>52</v>
       </c>
-      <c r="E44" t="s">
+      <c r="D44" t="s">
         <v>256</v>
       </c>
       <c r="F44" t="s">
         <v>256</v>
       </c>
-      <c r="L44" t="s">
-        <v>256</v>
-      </c>
-      <c r="N44" t="s">
+      <c r="G44" t="s">
+        <v>256</v>
+      </c>
+      <c r="M44" t="s">
         <v>256</v>
       </c>
       <c r="O44" t="s">
@@ -8083,7 +8149,7 @@
       <c r="P44" t="s">
         <v>256</v>
       </c>
-      <c r="R44" t="s">
+      <c r="Q44" t="s">
         <v>256</v>
       </c>
       <c r="S44" t="s">
@@ -8095,7 +8161,7 @@
       <c r="U44" t="s">
         <v>256</v>
       </c>
-      <c r="W44" t="s">
+      <c r="V44" t="s">
         <v>256</v>
       </c>
       <c r="X44" t="s">
@@ -8107,53 +8173,53 @@
       <c r="Z44" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="45" spans="1:26">
+      <c r="AA44" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27">
       <c r="A45" t="s">
         <v>53</v>
       </c>
-      <c r="P45" t="s">
-        <v>256</v>
-      </c>
-      <c r="R45" t="s">
-        <v>256</v>
-      </c>
-      <c r="U45" t="s">
-        <v>256</v>
-      </c>
-      <c r="W45" t="s">
-        <v>256</v>
-      </c>
-      <c r="Z45" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="46" spans="1:26">
+      <c r="Q45" t="s">
+        <v>256</v>
+      </c>
+      <c r="S45" t="s">
+        <v>256</v>
+      </c>
+      <c r="V45" t="s">
+        <v>256</v>
+      </c>
+      <c r="X45" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27">
       <c r="A46" t="s">
         <v>54</v>
       </c>
-      <c r="E46" t="s">
-        <v>256</v>
-      </c>
-      <c r="J46" t="s">
-        <v>256</v>
-      </c>
-      <c r="L46" t="s">
-        <v>256</v>
-      </c>
-      <c r="P46" t="s">
-        <v>256</v>
-      </c>
-      <c r="R46" t="s">
-        <v>256</v>
-      </c>
-      <c r="T46" t="s">
+      <c r="F46" t="s">
+        <v>256</v>
+      </c>
+      <c r="K46" t="s">
+        <v>256</v>
+      </c>
+      <c r="M46" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>256</v>
+      </c>
+      <c r="S46" t="s">
         <v>256</v>
       </c>
       <c r="U46" t="s">
         <v>256</v>
       </c>
-      <c r="W46" t="s">
+      <c r="V46" t="s">
         <v>256</v>
       </c>
       <c r="X46" t="s">
@@ -8165,24 +8231,27 @@
       <c r="Z46" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="47" spans="1:26">
+      <c r="AA46" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="47" spans="1:27">
       <c r="A47" t="s">
         <v>55</v>
       </c>
-      <c r="E47" t="s">
+      <c r="D47" t="s">
         <v>256</v>
       </c>
       <c r="F47" t="s">
         <v>256</v>
       </c>
-      <c r="I47" t="s">
-        <v>256</v>
-      </c>
-      <c r="L47" t="s">
-        <v>256</v>
-      </c>
-      <c r="N47" t="s">
+      <c r="G47" t="s">
+        <v>256</v>
+      </c>
+      <c r="J47" t="s">
+        <v>256</v>
+      </c>
+      <c r="M47" t="s">
         <v>256</v>
       </c>
       <c r="O47" t="s">
@@ -8191,7 +8260,7 @@
       <c r="P47" t="s">
         <v>256</v>
       </c>
-      <c r="R47" t="s">
+      <c r="Q47" t="s">
         <v>256</v>
       </c>
       <c r="S47" t="s">
@@ -8203,7 +8272,7 @@
       <c r="U47" t="s">
         <v>256</v>
       </c>
-      <c r="W47" t="s">
+      <c r="V47" t="s">
         <v>256</v>
       </c>
       <c r="X47" t="s">
@@ -8215,30 +8284,30 @@
       <c r="Z47" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="48" spans="1:26">
+      <c r="AA47" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="48" spans="1:27">
       <c r="A48" t="s">
         <v>56</v>
       </c>
       <c r="B48" t="s">
         <v>256</v>
       </c>
-      <c r="L48" t="s">
-        <v>256</v>
-      </c>
-      <c r="P48" t="s">
-        <v>256</v>
-      </c>
-      <c r="R48" t="s">
+      <c r="M48" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q48" t="s">
         <v>256</v>
       </c>
       <c r="S48" t="s">
         <v>256</v>
       </c>
-      <c r="U48" t="s">
-        <v>256</v>
-      </c>
-      <c r="W48" t="s">
+      <c r="T48" t="s">
+        <v>256</v>
+      </c>
+      <c r="V48" t="s">
         <v>256</v>
       </c>
       <c r="X48" t="s">
@@ -8250,27 +8319,27 @@
       <c r="Z48" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="49" spans="1:26">
+      <c r="AA48" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27">
       <c r="A49" t="s">
         <v>57</v>
       </c>
       <c r="C49" t="s">
         <v>256</v>
       </c>
-      <c r="E49" t="s">
-        <v>256</v>
-      </c>
       <c r="F49" t="s">
         <v>256</v>
       </c>
-      <c r="L49" t="s">
-        <v>256</v>
-      </c>
-      <c r="N49" t="s">
-        <v>256</v>
-      </c>
-      <c r="P49" t="s">
+      <c r="G49" t="s">
+        <v>256</v>
+      </c>
+      <c r="M49" t="s">
+        <v>256</v>
+      </c>
+      <c r="O49" t="s">
         <v>256</v>
       </c>
       <c r="Q49" t="s">
@@ -8288,7 +8357,7 @@
       <c r="U49" t="s">
         <v>256</v>
       </c>
-      <c r="W49" t="s">
+      <c r="V49" t="s">
         <v>256</v>
       </c>
       <c r="X49" t="s">
@@ -8300,8 +8369,11 @@
       <c r="Z49" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="50" spans="1:26">
+      <c r="AA49" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27">
       <c r="A50" t="s">
         <v>58</v>
       </c>
@@ -8314,7 +8386,7 @@
       <c r="F50" t="s">
         <v>256</v>
       </c>
-      <c r="H50" t="s">
+      <c r="G50" t="s">
         <v>256</v>
       </c>
       <c r="I50" t="s">
@@ -8323,25 +8395,25 @@
       <c r="J50" t="s">
         <v>256</v>
       </c>
-      <c r="L50" t="s">
-        <v>256</v>
-      </c>
-      <c r="O50" t="s">
+      <c r="K50" t="s">
+        <v>256</v>
+      </c>
+      <c r="M50" t="s">
         <v>256</v>
       </c>
       <c r="P50" t="s">
         <v>256</v>
       </c>
-      <c r="R50" t="s">
-        <v>256</v>
-      </c>
-      <c r="T50" t="s">
+      <c r="Q50" t="s">
+        <v>256</v>
+      </c>
+      <c r="S50" t="s">
         <v>256</v>
       </c>
       <c r="U50" t="s">
         <v>256</v>
       </c>
-      <c r="W50" t="s">
+      <c r="V50" t="s">
         <v>256</v>
       </c>
       <c r="X50" t="s">
@@ -8353,8 +8425,11 @@
       <c r="Z50" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="51" spans="1:26">
+      <c r="AA50" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27">
       <c r="A51" t="s">
         <v>59</v>
       </c>
@@ -8367,19 +8442,19 @@
       <c r="F51" t="s">
         <v>256</v>
       </c>
-      <c r="J51" t="s">
-        <v>256</v>
-      </c>
-      <c r="L51" t="s">
-        <v>256</v>
-      </c>
-      <c r="O51" t="s">
+      <c r="G51" t="s">
+        <v>256</v>
+      </c>
+      <c r="K51" t="s">
+        <v>256</v>
+      </c>
+      <c r="M51" t="s">
         <v>256</v>
       </c>
       <c r="P51" t="s">
         <v>256</v>
       </c>
-      <c r="R51" t="s">
+      <c r="Q51" t="s">
         <v>256</v>
       </c>
       <c r="S51" t="s">
@@ -8391,7 +8466,7 @@
       <c r="U51" t="s">
         <v>256</v>
       </c>
-      <c r="W51" t="s">
+      <c r="V51" t="s">
         <v>256</v>
       </c>
       <c r="X51" t="s">
@@ -8403,18 +8478,18 @@
       <c r="Z51" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="52" spans="1:26">
+      <c r="AA51" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27">
       <c r="A52" t="s">
         <v>60</v>
       </c>
       <c r="B52" t="s">
         <v>256</v>
       </c>
-      <c r="L52" t="s">
-        <v>256</v>
-      </c>
-      <c r="P52" t="s">
+      <c r="M52" t="s">
         <v>256</v>
       </c>
       <c r="Q52" t="s">
@@ -8429,7 +8504,7 @@
       <c r="T52" t="s">
         <v>256</v>
       </c>
-      <c r="W52" t="s">
+      <c r="U52" t="s">
         <v>256</v>
       </c>
       <c r="X52" t="s">
@@ -8441,24 +8516,27 @@
       <c r="Z52" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="53" spans="1:26">
+      <c r="AA52" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27">
       <c r="A53" t="s">
         <v>61</v>
       </c>
       <c r="C53" t="s">
         <v>256</v>
       </c>
-      <c r="E53" t="s">
+      <c r="D53" t="s">
         <v>256</v>
       </c>
       <c r="F53" t="s">
         <v>256</v>
       </c>
-      <c r="L53" t="s">
-        <v>256</v>
-      </c>
-      <c r="O53" t="s">
+      <c r="G53" t="s">
+        <v>256</v>
+      </c>
+      <c r="M53" t="s">
         <v>256</v>
       </c>
       <c r="P53" t="s">
@@ -8479,7 +8557,7 @@
       <c r="U53" t="s">
         <v>256</v>
       </c>
-      <c r="W53" t="s">
+      <c r="V53" t="s">
         <v>256</v>
       </c>
       <c r="X53" t="s">
@@ -8491,27 +8569,30 @@
       <c r="Z53" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="54" spans="1:26">
+      <c r="AA53" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27">
       <c r="A54" t="s">
         <v>62</v>
       </c>
-      <c r="E54" t="s">
+      <c r="D54" t="s">
         <v>256</v>
       </c>
       <c r="F54" t="s">
         <v>256</v>
       </c>
-      <c r="J54" t="s">
-        <v>256</v>
-      </c>
-      <c r="O54" t="s">
+      <c r="G54" t="s">
+        <v>256</v>
+      </c>
+      <c r="K54" t="s">
         <v>256</v>
       </c>
       <c r="P54" t="s">
         <v>256</v>
       </c>
-      <c r="S54" t="s">
+      <c r="Q54" t="s">
         <v>256</v>
       </c>
       <c r="T54" t="s">
@@ -8520,36 +8601,36 @@
       <c r="U54" t="s">
         <v>256</v>
       </c>
-      <c r="W54" t="s">
+      <c r="V54" t="s">
         <v>256</v>
       </c>
       <c r="X54" t="s">
         <v>256</v>
       </c>
-      <c r="Z54" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="55" spans="1:26">
+      <c r="Y54" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27">
       <c r="A55" t="s">
         <v>64</v>
       </c>
-      <c r="E55" t="s">
-        <v>256</v>
-      </c>
       <c r="F55" t="s">
         <v>256</v>
       </c>
-      <c r="P55" t="s">
-        <v>256</v>
-      </c>
-      <c r="T55" t="s">
+      <c r="G55" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q55" t="s">
         <v>256</v>
       </c>
       <c r="U55" t="s">
         <v>256</v>
       </c>
-      <c r="W55" t="s">
+      <c r="V55" t="s">
         <v>256</v>
       </c>
       <c r="X55" t="s">
@@ -8561,24 +8642,24 @@
       <c r="Z55" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="56" spans="1:26">
+      <c r="AA55" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27">
       <c r="A56" t="s">
         <v>65</v>
       </c>
       <c r="B56" t="s">
         <v>256</v>
       </c>
-      <c r="F56" t="s">
-        <v>256</v>
-      </c>
-      <c r="L56" t="s">
-        <v>256</v>
-      </c>
-      <c r="P56" t="s">
-        <v>256</v>
-      </c>
-      <c r="R56" t="s">
+      <c r="G56" t="s">
+        <v>256</v>
+      </c>
+      <c r="M56" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q56" t="s">
         <v>256</v>
       </c>
       <c r="S56" t="s">
@@ -8590,7 +8671,7 @@
       <c r="U56" t="s">
         <v>256</v>
       </c>
-      <c r="W56" t="s">
+      <c r="V56" t="s">
         <v>256</v>
       </c>
       <c r="X56" t="s">
@@ -8602,8 +8683,11 @@
       <c r="Z56" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="57" spans="1:26">
+      <c r="AA56" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="57" spans="1:27">
       <c r="A57" t="s">
         <v>66</v>
       </c>
@@ -8616,10 +8700,10 @@
       <c r="F57" t="s">
         <v>256</v>
       </c>
-      <c r="L57" t="s">
-        <v>256</v>
-      </c>
-      <c r="N57" t="s">
+      <c r="G57" t="s">
+        <v>256</v>
+      </c>
+      <c r="M57" t="s">
         <v>256</v>
       </c>
       <c r="O57" t="s">
@@ -8628,16 +8712,16 @@
       <c r="P57" t="s">
         <v>256</v>
       </c>
-      <c r="R57" t="s">
-        <v>256</v>
-      </c>
-      <c r="T57" t="s">
+      <c r="Q57" t="s">
+        <v>256</v>
+      </c>
+      <c r="S57" t="s">
         <v>256</v>
       </c>
       <c r="U57" t="s">
         <v>256</v>
       </c>
-      <c r="W57" t="s">
+      <c r="V57" t="s">
         <v>256</v>
       </c>
       <c r="X57" t="s">
@@ -8649,8 +8733,11 @@
       <c r="Z57" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="58" spans="1:26">
+      <c r="AA57" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="58" spans="1:27">
       <c r="A58" t="s">
         <v>67</v>
       </c>
@@ -8660,47 +8747,47 @@
       <c r="C58" t="s">
         <v>256</v>
       </c>
-      <c r="D58" t="s">
-        <v>256</v>
-      </c>
       <c r="E58" t="s">
         <v>256</v>
       </c>
       <c r="F58" t="s">
         <v>256</v>
       </c>
-      <c r="H58" t="s">
+      <c r="G58" t="s">
         <v>256</v>
       </c>
       <c r="I58" t="s">
         <v>256</v>
       </c>
-      <c r="L58" t="s">
-        <v>256</v>
-      </c>
-      <c r="P58" t="s">
-        <v>256</v>
-      </c>
-      <c r="R58" t="s">
-        <v>256</v>
-      </c>
-      <c r="T58" t="s">
+      <c r="J58" t="s">
+        <v>256</v>
+      </c>
+      <c r="M58" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>256</v>
+      </c>
+      <c r="S58" t="s">
         <v>256</v>
       </c>
       <c r="U58" t="s">
         <v>256</v>
       </c>
-      <c r="W58" t="s">
+      <c r="V58" t="s">
         <v>256</v>
       </c>
       <c r="X58" t="s">
         <v>256</v>
       </c>
-      <c r="Z58" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="59" spans="1:26">
+      <c r="Y58" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA58" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="59" spans="1:27">
       <c r="A59" t="s">
         <v>68</v>
       </c>
@@ -8716,7 +8803,7 @@
       <c r="F59" t="s">
         <v>256</v>
       </c>
-      <c r="H59" t="s">
+      <c r="G59" t="s">
         <v>256</v>
       </c>
       <c r="I59" t="s">
@@ -8725,16 +8812,16 @@
       <c r="J59" t="s">
         <v>256</v>
       </c>
-      <c r="L59" t="s">
-        <v>256</v>
-      </c>
-      <c r="O59" t="s">
+      <c r="K59" t="s">
+        <v>256</v>
+      </c>
+      <c r="M59" t="s">
         <v>256</v>
       </c>
       <c r="P59" t="s">
         <v>256</v>
       </c>
-      <c r="S59" t="s">
+      <c r="Q59" t="s">
         <v>256</v>
       </c>
       <c r="T59" t="s">
@@ -8743,7 +8830,7 @@
       <c r="U59" t="s">
         <v>256</v>
       </c>
-      <c r="W59" t="s">
+      <c r="V59" t="s">
         <v>256</v>
       </c>
       <c r="X59" t="s">
@@ -8755,30 +8842,30 @@
       <c r="Z59" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="60" spans="1:26">
+      <c r="AA59" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="60" spans="1:27">
       <c r="A60" t="s">
         <v>69</v>
       </c>
-      <c r="E60" t="s">
-        <v>256</v>
-      </c>
       <c r="F60" t="s">
         <v>256</v>
       </c>
-      <c r="H60" t="s">
-        <v>256</v>
-      </c>
-      <c r="J60" t="s">
-        <v>256</v>
-      </c>
-      <c r="L60" t="s">
-        <v>256</v>
-      </c>
-      <c r="P60" t="s">
-        <v>256</v>
-      </c>
-      <c r="R60" t="s">
+      <c r="G60" t="s">
+        <v>256</v>
+      </c>
+      <c r="I60" t="s">
+        <v>256</v>
+      </c>
+      <c r="K60" t="s">
+        <v>256</v>
+      </c>
+      <c r="M60" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q60" t="s">
         <v>256</v>
       </c>
       <c r="S60" t="s">
@@ -8790,7 +8877,7 @@
       <c r="U60" t="s">
         <v>256</v>
       </c>
-      <c r="W60" t="s">
+      <c r="V60" t="s">
         <v>256</v>
       </c>
       <c r="X60" t="s">
@@ -8802,8 +8889,11 @@
       <c r="Z60" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="61" spans="1:26">
+      <c r="AA60" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="61" spans="1:27">
       <c r="A61" t="s">
         <v>70</v>
       </c>
@@ -8819,7 +8909,7 @@
       <c r="F61" t="s">
         <v>256</v>
       </c>
-      <c r="H61" t="s">
+      <c r="G61" t="s">
         <v>256</v>
       </c>
       <c r="I61" t="s">
@@ -8828,16 +8918,16 @@
       <c r="J61" t="s">
         <v>256</v>
       </c>
-      <c r="L61" t="s">
-        <v>256</v>
-      </c>
-      <c r="O61" t="s">
+      <c r="K61" t="s">
+        <v>256</v>
+      </c>
+      <c r="M61" t="s">
         <v>256</v>
       </c>
       <c r="P61" t="s">
         <v>256</v>
       </c>
-      <c r="S61" t="s">
+      <c r="Q61" t="s">
         <v>256</v>
       </c>
       <c r="T61" t="s">
@@ -8846,17 +8936,20 @@
       <c r="U61" t="s">
         <v>256</v>
       </c>
-      <c r="W61" t="s">
+      <c r="V61" t="s">
         <v>256</v>
       </c>
       <c r="X61" t="s">
         <v>256</v>
       </c>
-      <c r="Z61" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="62" spans="1:26">
+      <c r="Y61" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA61" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="62" spans="1:27">
       <c r="A62" t="s">
         <v>71</v>
       </c>
@@ -8869,34 +8962,34 @@
       <c r="D62" t="s">
         <v>256</v>
       </c>
-      <c r="F62" t="s">
-        <v>256</v>
-      </c>
-      <c r="H62" t="s">
-        <v>256</v>
-      </c>
-      <c r="J62" t="s">
-        <v>256</v>
-      </c>
-      <c r="L62" t="s">
-        <v>256</v>
-      </c>
-      <c r="O62" t="s">
+      <c r="E62" t="s">
+        <v>256</v>
+      </c>
+      <c r="G62" t="s">
+        <v>256</v>
+      </c>
+      <c r="I62" t="s">
+        <v>256</v>
+      </c>
+      <c r="K62" t="s">
+        <v>256</v>
+      </c>
+      <c r="M62" t="s">
         <v>256</v>
       </c>
       <c r="P62" t="s">
         <v>256</v>
       </c>
-      <c r="R62" t="s">
-        <v>256</v>
-      </c>
-      <c r="T62" t="s">
+      <c r="Q62" t="s">
+        <v>256</v>
+      </c>
+      <c r="S62" t="s">
         <v>256</v>
       </c>
       <c r="U62" t="s">
         <v>256</v>
       </c>
-      <c r="W62" t="s">
+      <c r="V62" t="s">
         <v>256</v>
       </c>
       <c r="X62" t="s">
@@ -8908,27 +9001,30 @@
       <c r="Z62" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="63" spans="1:26">
+      <c r="AA62" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="63" spans="1:27">
       <c r="A63" t="s">
         <v>72</v>
       </c>
-      <c r="E63" t="s">
+      <c r="D63" t="s">
         <v>256</v>
       </c>
       <c r="F63" t="s">
         <v>256</v>
       </c>
-      <c r="L63" t="s">
-        <v>256</v>
-      </c>
-      <c r="O63" t="s">
+      <c r="G63" t="s">
+        <v>256</v>
+      </c>
+      <c r="M63" t="s">
         <v>256</v>
       </c>
       <c r="P63" t="s">
         <v>256</v>
       </c>
-      <c r="R63" t="s">
+      <c r="Q63" t="s">
         <v>256</v>
       </c>
       <c r="S63" t="s">
@@ -8940,7 +9036,7 @@
       <c r="U63" t="s">
         <v>256</v>
       </c>
-      <c r="W63" t="s">
+      <c r="V63" t="s">
         <v>256</v>
       </c>
       <c r="X63" t="s">
@@ -8952,21 +9048,24 @@
       <c r="Z63" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="64" spans="1:26">
+      <c r="AA63" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="64" spans="1:27">
       <c r="A64" t="s">
         <v>73</v>
       </c>
-      <c r="E64" t="s">
+      <c r="D64" t="s">
         <v>256</v>
       </c>
       <c r="F64" t="s">
         <v>256</v>
       </c>
-      <c r="L64" t="s">
-        <v>256</v>
-      </c>
-      <c r="N64" t="s">
+      <c r="G64" t="s">
+        <v>256</v>
+      </c>
+      <c r="M64" t="s">
         <v>256</v>
       </c>
       <c r="O64" t="s">
@@ -8975,7 +9074,7 @@
       <c r="P64" t="s">
         <v>256</v>
       </c>
-      <c r="S64" t="s">
+      <c r="Q64" t="s">
         <v>256</v>
       </c>
       <c r="T64" t="s">
@@ -8984,7 +9083,7 @@
       <c r="U64" t="s">
         <v>256</v>
       </c>
-      <c r="W64" t="s">
+      <c r="V64" t="s">
         <v>256</v>
       </c>
       <c r="X64" t="s">
@@ -8996,21 +9095,24 @@
       <c r="Z64" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="65" spans="1:26">
+      <c r="AA64" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="65" spans="1:27">
       <c r="A65" t="s">
         <v>74</v>
       </c>
       <c r="B65" t="s">
         <v>256</v>
       </c>
-      <c r="J65" t="s">
-        <v>256</v>
-      </c>
-      <c r="L65" t="s">
-        <v>256</v>
-      </c>
-      <c r="O65" t="s">
+      <c r="D65" t="s">
+        <v>256</v>
+      </c>
+      <c r="K65" t="s">
+        <v>256</v>
+      </c>
+      <c r="M65" t="s">
         <v>256</v>
       </c>
       <c r="P65" t="s">
@@ -9022,40 +9124,46 @@
       <c r="R65" t="s">
         <v>256</v>
       </c>
-      <c r="U65" t="s">
-        <v>256</v>
-      </c>
-      <c r="W65" t="s">
+      <c r="S65" t="s">
+        <v>256</v>
+      </c>
+      <c r="V65" t="s">
         <v>256</v>
       </c>
       <c r="X65" t="s">
         <v>256</v>
       </c>
-      <c r="Z65" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="66" spans="1:26">
+      <c r="Y65" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA65" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="66" spans="1:27">
       <c r="A66" t="s">
         <v>75</v>
       </c>
-      <c r="O66" t="s">
+      <c r="D66" t="s">
         <v>256</v>
       </c>
       <c r="P66" t="s">
         <v>256</v>
       </c>
-      <c r="R66" t="s">
-        <v>256</v>
-      </c>
-      <c r="W66" t="s">
-        <v>256</v>
-      </c>
-      <c r="Z66" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="67" spans="1:26">
+      <c r="Q66" t="s">
+        <v>256</v>
+      </c>
+      <c r="S66" t="s">
+        <v>256</v>
+      </c>
+      <c r="X66" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA66" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="67" spans="1:27">
       <c r="A67" t="s">
         <v>76</v>
       </c>
@@ -9065,10 +9173,10 @@
       <c r="D67" t="s">
         <v>256</v>
       </c>
-      <c r="F67" t="s">
-        <v>256</v>
-      </c>
-      <c r="H67" t="s">
+      <c r="E67" t="s">
+        <v>256</v>
+      </c>
+      <c r="G67" t="s">
         <v>256</v>
       </c>
       <c r="I67" t="s">
@@ -9077,16 +9185,16 @@
       <c r="J67" t="s">
         <v>256</v>
       </c>
-      <c r="L67" t="s">
-        <v>256</v>
-      </c>
-      <c r="O67" t="s">
+      <c r="K67" t="s">
+        <v>256</v>
+      </c>
+      <c r="M67" t="s">
         <v>256</v>
       </c>
       <c r="P67" t="s">
         <v>256</v>
       </c>
-      <c r="S67" t="s">
+      <c r="Q67" t="s">
         <v>256</v>
       </c>
       <c r="T67" t="s">
@@ -9095,7 +9203,7 @@
       <c r="U67" t="s">
         <v>256</v>
       </c>
-      <c r="W67" t="s">
+      <c r="V67" t="s">
         <v>256</v>
       </c>
       <c r="X67" t="s">
@@ -9107,8 +9215,11 @@
       <c r="Z67" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="68" spans="1:26">
+      <c r="AA67" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="68" spans="1:27">
       <c r="A68" t="s">
         <v>78</v>
       </c>
@@ -9118,22 +9229,22 @@
       <c r="D68" t="s">
         <v>256</v>
       </c>
-      <c r="F68" t="s">
-        <v>256</v>
-      </c>
-      <c r="H68" t="s">
-        <v>256</v>
-      </c>
-      <c r="L68" t="s">
-        <v>256</v>
-      </c>
-      <c r="O68" t="s">
+      <c r="E68" t="s">
+        <v>256</v>
+      </c>
+      <c r="G68" t="s">
+        <v>256</v>
+      </c>
+      <c r="I68" t="s">
+        <v>256</v>
+      </c>
+      <c r="M68" t="s">
         <v>256</v>
       </c>
       <c r="P68" t="s">
         <v>256</v>
       </c>
-      <c r="S68" t="s">
+      <c r="Q68" t="s">
         <v>256</v>
       </c>
       <c r="T68" t="s">
@@ -9142,7 +9253,7 @@
       <c r="U68" t="s">
         <v>256</v>
       </c>
-      <c r="W68" t="s">
+      <c r="V68" t="s">
         <v>256</v>
       </c>
       <c r="X68" t="s">
@@ -9154,30 +9265,30 @@
       <c r="Z68" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="69" spans="1:26">
+      <c r="AA68" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="69" spans="1:27">
       <c r="A69" t="s">
         <v>79</v>
       </c>
       <c r="B69" t="s">
         <v>256</v>
       </c>
-      <c r="D69" t="s">
-        <v>256</v>
-      </c>
       <c r="E69" t="s">
         <v>256</v>
       </c>
-      <c r="H69" t="s">
-        <v>256</v>
-      </c>
-      <c r="J69" t="s">
-        <v>256</v>
-      </c>
-      <c r="P69" t="s">
-        <v>256</v>
-      </c>
-      <c r="R69" t="s">
+      <c r="F69" t="s">
+        <v>256</v>
+      </c>
+      <c r="I69" t="s">
+        <v>256</v>
+      </c>
+      <c r="K69" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q69" t="s">
         <v>256</v>
       </c>
       <c r="S69" t="s">
@@ -9189,37 +9300,40 @@
       <c r="U69" t="s">
         <v>256</v>
       </c>
-      <c r="X69" t="s">
-        <v>256</v>
-      </c>
-      <c r="Z69" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="70" spans="1:26">
+      <c r="V69" t="s">
+        <v>256</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA69" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="70" spans="1:27">
       <c r="A70" t="s">
         <v>81</v>
       </c>
-      <c r="L70" t="s">
-        <v>256</v>
-      </c>
-      <c r="P70" t="s">
-        <v>256</v>
-      </c>
-      <c r="R70" t="s">
-        <v>256</v>
-      </c>
-      <c r="U70" t="s">
-        <v>256</v>
-      </c>
-      <c r="Y70" t="s">
+      <c r="M70" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>256</v>
+      </c>
+      <c r="S70" t="s">
+        <v>256</v>
+      </c>
+      <c r="V70" t="s">
         <v>256</v>
       </c>
       <c r="Z70" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="71" spans="1:26">
+      <c r="AA70" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="71" spans="1:27">
       <c r="A71" t="s">
         <v>82</v>
       </c>
@@ -9235,19 +9349,19 @@
       <c r="F71" t="s">
         <v>256</v>
       </c>
-      <c r="J71" t="s">
-        <v>256</v>
-      </c>
-      <c r="L71" t="s">
-        <v>256</v>
-      </c>
-      <c r="O71" t="s">
+      <c r="G71" t="s">
+        <v>256</v>
+      </c>
+      <c r="K71" t="s">
+        <v>256</v>
+      </c>
+      <c r="M71" t="s">
         <v>256</v>
       </c>
       <c r="P71" t="s">
         <v>256</v>
       </c>
-      <c r="R71" t="s">
+      <c r="Q71" t="s">
         <v>256</v>
       </c>
       <c r="S71" t="s">
@@ -9259,7 +9373,7 @@
       <c r="U71" t="s">
         <v>256</v>
       </c>
-      <c r="W71" t="s">
+      <c r="V71" t="s">
         <v>256</v>
       </c>
       <c r="X71" t="s">
@@ -9271,8 +9385,11 @@
       <c r="Z71" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="72" spans="1:26">
+      <c r="AA71" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="72" spans="1:27">
       <c r="A72" t="s">
         <v>83</v>
       </c>
@@ -9288,19 +9405,19 @@
       <c r="F72" t="s">
         <v>256</v>
       </c>
-      <c r="I72" t="s">
-        <v>256</v>
-      </c>
-      <c r="L72" t="s">
-        <v>256</v>
-      </c>
-      <c r="O72" t="s">
+      <c r="G72" t="s">
+        <v>256</v>
+      </c>
+      <c r="J72" t="s">
+        <v>256</v>
+      </c>
+      <c r="M72" t="s">
         <v>256</v>
       </c>
       <c r="P72" t="s">
         <v>256</v>
       </c>
-      <c r="R72" t="s">
+      <c r="Q72" t="s">
         <v>256</v>
       </c>
       <c r="S72" t="s">
@@ -9312,7 +9429,7 @@
       <c r="U72" t="s">
         <v>256</v>
       </c>
-      <c r="W72" t="s">
+      <c r="V72" t="s">
         <v>256</v>
       </c>
       <c r="X72" t="s">
@@ -9324,21 +9441,21 @@
       <c r="Z72" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="73" spans="1:26">
+      <c r="AA72" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="73" spans="1:27">
       <c r="A73" t="s">
         <v>84</v>
       </c>
-      <c r="E73" t="s">
-        <v>256</v>
-      </c>
       <c r="F73" t="s">
         <v>256</v>
       </c>
-      <c r="L73" t="s">
-        <v>256</v>
-      </c>
-      <c r="P73" t="s">
+      <c r="G73" t="s">
+        <v>256</v>
+      </c>
+      <c r="M73" t="s">
         <v>256</v>
       </c>
       <c r="Q73" t="s">
@@ -9356,7 +9473,7 @@
       <c r="U73" t="s">
         <v>256</v>
       </c>
-      <c r="W73" t="s">
+      <c r="V73" t="s">
         <v>256</v>
       </c>
       <c r="X73" t="s">
@@ -9368,27 +9485,30 @@
       <c r="Z73" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="74" spans="1:26">
+      <c r="AA73" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="74" spans="1:27">
       <c r="A74" t="s">
         <v>85</v>
       </c>
-      <c r="E74" t="s">
+      <c r="D74" t="s">
         <v>256</v>
       </c>
       <c r="F74" t="s">
         <v>256</v>
       </c>
-      <c r="L74" t="s">
-        <v>256</v>
-      </c>
-      <c r="O74" t="s">
+      <c r="G74" t="s">
+        <v>256</v>
+      </c>
+      <c r="M74" t="s">
         <v>256</v>
       </c>
       <c r="P74" t="s">
         <v>256</v>
       </c>
-      <c r="S74" t="s">
+      <c r="Q74" t="s">
         <v>256</v>
       </c>
       <c r="T74" t="s">
@@ -9397,7 +9517,7 @@
       <c r="U74" t="s">
         <v>256</v>
       </c>
-      <c r="W74" t="s">
+      <c r="V74" t="s">
         <v>256</v>
       </c>
       <c r="X74" t="s">
@@ -9409,67 +9529,67 @@
       <c r="Z74" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="75" spans="1:26">
+      <c r="AA74" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="75" spans="1:27">
       <c r="A75" t="s">
         <v>86</v>
       </c>
       <c r="B75" t="s">
         <v>256</v>
       </c>
-      <c r="F75" t="s">
-        <v>256</v>
-      </c>
-      <c r="P75" t="s">
+      <c r="G75" t="s">
         <v>256</v>
       </c>
       <c r="Q75" t="s">
         <v>256</v>
       </c>
-      <c r="T75" t="s">
+      <c r="R75" t="s">
         <v>256</v>
       </c>
       <c r="U75" t="s">
         <v>256</v>
       </c>
-      <c r="W75" t="s">
+      <c r="V75" t="s">
         <v>256</v>
       </c>
       <c r="X75" t="s">
         <v>256</v>
       </c>
-      <c r="Z75" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="76" spans="1:26">
+      <c r="Y75" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA75" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="76" spans="1:27">
       <c r="A76" t="s">
         <v>87</v>
       </c>
-      <c r="P76" t="s">
-        <v>256</v>
-      </c>
-      <c r="S76" t="s">
-        <v>256</v>
-      </c>
-      <c r="W76" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="77" spans="1:26">
+      <c r="Q76" t="s">
+        <v>256</v>
+      </c>
+      <c r="T76" t="s">
+        <v>256</v>
+      </c>
+      <c r="X76" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="77" spans="1:27">
       <c r="A77" t="s">
         <v>88</v>
       </c>
-      <c r="E77" t="s">
-        <v>256</v>
-      </c>
       <c r="F77" t="s">
         <v>256</v>
       </c>
-      <c r="L77" t="s">
-        <v>256</v>
-      </c>
-      <c r="P77" t="s">
+      <c r="G77" t="s">
+        <v>256</v>
+      </c>
+      <c r="M77" t="s">
         <v>256</v>
       </c>
       <c r="Q77" t="s">
@@ -9502,21 +9622,21 @@
       <c r="Z77" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="78" spans="1:26">
+      <c r="AA77" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="78" spans="1:27">
       <c r="A78" t="s">
         <v>89</v>
       </c>
-      <c r="E78" t="s">
-        <v>256</v>
-      </c>
       <c r="F78" t="s">
         <v>256</v>
       </c>
-      <c r="L78" t="s">
-        <v>256</v>
-      </c>
-      <c r="P78" t="s">
+      <c r="G78" t="s">
+        <v>256</v>
+      </c>
+      <c r="M78" t="s">
         <v>256</v>
       </c>
       <c r="Q78" t="s">
@@ -9534,7 +9654,7 @@
       <c r="U78" t="s">
         <v>256</v>
       </c>
-      <c r="W78" t="s">
+      <c r="V78" t="s">
         <v>256</v>
       </c>
       <c r="X78" t="s">
@@ -9546,24 +9666,24 @@
       <c r="Z78" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="79" spans="1:26">
+      <c r="AA78" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="79" spans="1:27">
       <c r="A79" t="s">
         <v>90</v>
       </c>
-      <c r="E79" t="s">
-        <v>256</v>
-      </c>
       <c r="F79" t="s">
         <v>256</v>
       </c>
-      <c r="L79" t="s">
-        <v>256</v>
-      </c>
-      <c r="P79" t="s">
-        <v>256</v>
-      </c>
-      <c r="R79" t="s">
+      <c r="G79" t="s">
+        <v>256</v>
+      </c>
+      <c r="M79" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q79" t="s">
         <v>256</v>
       </c>
       <c r="S79" t="s">
@@ -9575,7 +9695,7 @@
       <c r="U79" t="s">
         <v>256</v>
       </c>
-      <c r="W79" t="s">
+      <c r="V79" t="s">
         <v>256</v>
       </c>
       <c r="X79" t="s">
@@ -9587,21 +9707,21 @@
       <c r="Z79" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="80" spans="1:26">
+      <c r="AA79" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="80" spans="1:27">
       <c r="A80" t="s">
         <v>91</v>
       </c>
       <c r="C80" t="s">
         <v>256</v>
       </c>
-      <c r="E80" t="s">
-        <v>256</v>
-      </c>
       <c r="F80" t="s">
         <v>256</v>
       </c>
-      <c r="P80" t="s">
+      <c r="G80" t="s">
         <v>256</v>
       </c>
       <c r="Q80" t="s">
@@ -9619,7 +9739,7 @@
       <c r="U80" t="s">
         <v>256</v>
       </c>
-      <c r="W80" t="s">
+      <c r="V80" t="s">
         <v>256</v>
       </c>
       <c r="X80" t="s">
@@ -9631,24 +9751,24 @@
       <c r="Z80" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="81" spans="1:26">
+      <c r="AA80" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="81" spans="1:27">
       <c r="A81" t="s">
         <v>92</v>
       </c>
       <c r="C81" t="s">
         <v>256</v>
       </c>
-      <c r="E81" t="s">
-        <v>256</v>
-      </c>
       <c r="F81" t="s">
         <v>256</v>
       </c>
-      <c r="L81" t="s">
-        <v>256</v>
-      </c>
-      <c r="P81" t="s">
+      <c r="G81" t="s">
+        <v>256</v>
+      </c>
+      <c r="M81" t="s">
         <v>256</v>
       </c>
       <c r="Q81" t="s">
@@ -9681,24 +9801,27 @@
       <c r="Z81" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="82" spans="1:26">
+      <c r="AA81" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="82" spans="1:27">
       <c r="A82" t="s">
         <v>93</v>
       </c>
       <c r="C82" t="s">
         <v>256</v>
       </c>
-      <c r="E82" t="s">
+      <c r="D82" t="s">
         <v>256</v>
       </c>
       <c r="F82" t="s">
         <v>256</v>
       </c>
-      <c r="L82" t="s">
-        <v>256</v>
-      </c>
-      <c r="N82" t="s">
+      <c r="G82" t="s">
+        <v>256</v>
+      </c>
+      <c r="M82" t="s">
         <v>256</v>
       </c>
       <c r="O82" t="s">
@@ -9722,7 +9845,7 @@
       <c r="U82" t="s">
         <v>256</v>
       </c>
-      <c r="W82" t="s">
+      <c r="V82" t="s">
         <v>256</v>
       </c>
       <c r="X82" t="s">
@@ -9734,27 +9857,27 @@
       <c r="Z82" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="83" spans="1:26">
+      <c r="AA82" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="83" spans="1:27">
       <c r="A83" t="s">
         <v>94</v>
       </c>
       <c r="C83" t="s">
         <v>256</v>
       </c>
-      <c r="F83" t="s">
-        <v>256</v>
-      </c>
-      <c r="L83" t="s">
-        <v>256</v>
-      </c>
-      <c r="P83" t="s">
+      <c r="G83" t="s">
+        <v>256</v>
+      </c>
+      <c r="M83" t="s">
         <v>256</v>
       </c>
       <c r="Q83" t="s">
         <v>256</v>
       </c>
-      <c r="S83" t="s">
+      <c r="R83" t="s">
         <v>256</v>
       </c>
       <c r="T83" t="s">
@@ -9763,7 +9886,7 @@
       <c r="U83" t="s">
         <v>256</v>
       </c>
-      <c r="W83" t="s">
+      <c r="V83" t="s">
         <v>256</v>
       </c>
       <c r="X83" t="s">
@@ -9775,24 +9898,24 @@
       <c r="Z83" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="84" spans="1:26">
+      <c r="AA83" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="84" spans="1:27">
       <c r="A84" t="s">
         <v>95</v>
       </c>
       <c r="C84" t="s">
         <v>256</v>
       </c>
-      <c r="E84" t="s">
-        <v>256</v>
-      </c>
       <c r="F84" t="s">
         <v>256</v>
       </c>
-      <c r="L84" t="s">
-        <v>256</v>
-      </c>
-      <c r="P84" t="s">
+      <c r="G84" t="s">
+        <v>256</v>
+      </c>
+      <c r="M84" t="s">
         <v>256</v>
       </c>
       <c r="Q84" t="s">
@@ -9810,7 +9933,7 @@
       <c r="U84" t="s">
         <v>256</v>
       </c>
-      <c r="W84" t="s">
+      <c r="V84" t="s">
         <v>256</v>
       </c>
       <c r="X84" t="s">
@@ -9822,24 +9945,24 @@
       <c r="Z84" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="85" spans="1:26">
+      <c r="AA84" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="85" spans="1:27">
       <c r="A85" t="s">
         <v>96</v>
       </c>
-      <c r="E85" t="s">
-        <v>256</v>
-      </c>
       <c r="F85" t="s">
         <v>256</v>
       </c>
-      <c r="P85" t="s">
+      <c r="G85" t="s">
         <v>256</v>
       </c>
       <c r="Q85" t="s">
         <v>256</v>
       </c>
-      <c r="S85" t="s">
+      <c r="R85" t="s">
         <v>256</v>
       </c>
       <c r="T85" t="s">
@@ -9848,7 +9971,7 @@
       <c r="U85" t="s">
         <v>256</v>
       </c>
-      <c r="W85" t="s">
+      <c r="V85" t="s">
         <v>256</v>
       </c>
       <c r="X85" t="s">
@@ -9860,24 +9983,27 @@
       <c r="Z85" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="86" spans="1:26">
+      <c r="AA85" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="86" spans="1:27">
       <c r="A86" t="s">
         <v>97</v>
       </c>
       <c r="C86" t="s">
         <v>256</v>
       </c>
-      <c r="E86" t="s">
+      <c r="D86" t="s">
         <v>256</v>
       </c>
       <c r="F86" t="s">
         <v>256</v>
       </c>
-      <c r="L86" t="s">
-        <v>256</v>
-      </c>
-      <c r="O86" t="s">
+      <c r="G86" t="s">
+        <v>256</v>
+      </c>
+      <c r="M86" t="s">
         <v>256</v>
       </c>
       <c r="P86" t="s">
@@ -9898,7 +10024,7 @@
       <c r="U86" t="s">
         <v>256</v>
       </c>
-      <c r="W86" t="s">
+      <c r="V86" t="s">
         <v>256</v>
       </c>
       <c r="X86" t="s">
@@ -9910,24 +10036,24 @@
       <c r="Z86" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="87" spans="1:26">
+      <c r="AA86" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="87" spans="1:27">
       <c r="A87" t="s">
         <v>98</v>
       </c>
       <c r="C87" t="s">
         <v>256</v>
       </c>
-      <c r="E87" t="s">
-        <v>256</v>
-      </c>
       <c r="F87" t="s">
         <v>256</v>
       </c>
-      <c r="P87" t="s">
-        <v>256</v>
-      </c>
-      <c r="S87" t="s">
+      <c r="G87" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q87" t="s">
         <v>256</v>
       </c>
       <c r="T87" t="s">
@@ -9936,7 +10062,7 @@
       <c r="U87" t="s">
         <v>256</v>
       </c>
-      <c r="W87" t="s">
+      <c r="V87" t="s">
         <v>256</v>
       </c>
       <c r="X87" t="s">
@@ -9948,24 +10074,24 @@
       <c r="Z87" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="88" spans="1:26">
+      <c r="AA87" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="88" spans="1:27">
       <c r="A88" t="s">
         <v>99</v>
       </c>
-      <c r="E88" t="s">
-        <v>256</v>
-      </c>
       <c r="F88" t="s">
         <v>256</v>
       </c>
-      <c r="L88" t="s">
-        <v>256</v>
-      </c>
-      <c r="P88" t="s">
-        <v>256</v>
-      </c>
-      <c r="S88" t="s">
+      <c r="G88" t="s">
+        <v>256</v>
+      </c>
+      <c r="M88" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q88" t="s">
         <v>256</v>
       </c>
       <c r="T88" t="s">
@@ -9974,17 +10100,20 @@
       <c r="U88" t="s">
         <v>256</v>
       </c>
-      <c r="W88" t="s">
+      <c r="V88" t="s">
         <v>256</v>
       </c>
       <c r="X88" t="s">
         <v>256</v>
       </c>
-      <c r="Z88" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="89" spans="1:26">
+      <c r="Y88" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA88" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="89" spans="1:27">
       <c r="A89" t="s">
         <v>100</v>
       </c>
@@ -9997,19 +10126,19 @@
       <c r="F89" t="s">
         <v>256</v>
       </c>
-      <c r="H89" t="s">
-        <v>256</v>
-      </c>
-      <c r="L89" t="s">
-        <v>256</v>
-      </c>
-      <c r="O89" t="s">
+      <c r="G89" t="s">
+        <v>256</v>
+      </c>
+      <c r="I89" t="s">
+        <v>256</v>
+      </c>
+      <c r="M89" t="s">
         <v>256</v>
       </c>
       <c r="P89" t="s">
         <v>256</v>
       </c>
-      <c r="R89" t="s">
+      <c r="Q89" t="s">
         <v>256</v>
       </c>
       <c r="S89" t="s">
@@ -10021,7 +10150,7 @@
       <c r="U89" t="s">
         <v>256</v>
       </c>
-      <c r="W89" t="s">
+      <c r="V89" t="s">
         <v>256</v>
       </c>
       <c r="X89" t="s">
@@ -10033,8 +10162,11 @@
       <c r="Z89" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="90" spans="1:26">
+      <c r="AA89" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="90" spans="1:27">
       <c r="A90" t="s">
         <v>101</v>
       </c>
@@ -10044,16 +10176,13 @@
       <c r="C90" t="s">
         <v>256</v>
       </c>
-      <c r="E90" t="s">
-        <v>256</v>
-      </c>
       <c r="F90" t="s">
         <v>256</v>
       </c>
-      <c r="L90" t="s">
-        <v>256</v>
-      </c>
-      <c r="P90" t="s">
+      <c r="G90" t="s">
+        <v>256</v>
+      </c>
+      <c r="M90" t="s">
         <v>256</v>
       </c>
       <c r="Q90" t="s">
@@ -10071,7 +10200,7 @@
       <c r="U90" t="s">
         <v>256</v>
       </c>
-      <c r="W90" t="s">
+      <c r="V90" t="s">
         <v>256</v>
       </c>
       <c r="X90" t="s">
@@ -10083,21 +10212,21 @@
       <c r="Z90" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="91" spans="1:26">
+      <c r="AA90" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="91" spans="1:27">
       <c r="A91" t="s">
         <v>102</v>
       </c>
-      <c r="D91" t="s">
-        <v>256</v>
-      </c>
       <c r="E91" t="s">
         <v>256</v>
       </c>
-      <c r="H91" t="s">
-        <v>256</v>
-      </c>
-      <c r="P91" t="s">
+      <c r="F91" t="s">
+        <v>256</v>
+      </c>
+      <c r="I91" t="s">
         <v>256</v>
       </c>
       <c r="Q91" t="s">
@@ -10115,7 +10244,7 @@
       <c r="U91" t="s">
         <v>256</v>
       </c>
-      <c r="W91" t="s">
+      <c r="V91" t="s">
         <v>256</v>
       </c>
       <c r="X91" t="s">
@@ -10127,8 +10256,11 @@
       <c r="Z91" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="92" spans="1:26">
+      <c r="AA91" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="92" spans="1:27">
       <c r="A92" t="s">
         <v>103</v>
       </c>
@@ -10138,13 +10270,13 @@
       <c r="C92" t="s">
         <v>256</v>
       </c>
-      <c r="F92" t="s">
-        <v>256</v>
-      </c>
-      <c r="L92" t="s">
-        <v>256</v>
-      </c>
-      <c r="N92" t="s">
+      <c r="D92" t="s">
+        <v>256</v>
+      </c>
+      <c r="G92" t="s">
+        <v>256</v>
+      </c>
+      <c r="M92" t="s">
         <v>256</v>
       </c>
       <c r="O92" t="s">
@@ -10168,7 +10300,7 @@
       <c r="U92" t="s">
         <v>256</v>
       </c>
-      <c r="W92" t="s">
+      <c r="V92" t="s">
         <v>256</v>
       </c>
       <c r="X92" t="s">
@@ -10180,8 +10312,11 @@
       <c r="Z92" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="93" spans="1:26">
+      <c r="AA92" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="93" spans="1:27">
       <c r="A93" t="s">
         <v>104</v>
       </c>
@@ -10191,16 +10326,13 @@
       <c r="C93" t="s">
         <v>256</v>
       </c>
-      <c r="F93" t="s">
-        <v>256</v>
-      </c>
-      <c r="L93" t="s">
-        <v>256</v>
-      </c>
-      <c r="P93" t="s">
-        <v>256</v>
-      </c>
-      <c r="R93" t="s">
+      <c r="G93" t="s">
+        <v>256</v>
+      </c>
+      <c r="M93" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q93" t="s">
         <v>256</v>
       </c>
       <c r="S93" t="s">
@@ -10212,7 +10344,7 @@
       <c r="U93" t="s">
         <v>256</v>
       </c>
-      <c r="W93" t="s">
+      <c r="V93" t="s">
         <v>256</v>
       </c>
       <c r="X93" t="s">
@@ -10224,24 +10356,27 @@
       <c r="Z93" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="94" spans="1:26">
+      <c r="AA93" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="94" spans="1:27">
       <c r="A94" t="s">
         <v>105</v>
       </c>
       <c r="C94" t="s">
         <v>256</v>
       </c>
-      <c r="E94" t="s">
+      <c r="D94" t="s">
         <v>256</v>
       </c>
       <c r="F94" t="s">
         <v>256</v>
       </c>
-      <c r="L94" t="s">
-        <v>256</v>
-      </c>
-      <c r="O94" t="s">
+      <c r="G94" t="s">
+        <v>256</v>
+      </c>
+      <c r="M94" t="s">
         <v>256</v>
       </c>
       <c r="P94" t="s">
@@ -10262,7 +10397,7 @@
       <c r="U94" t="s">
         <v>256</v>
       </c>
-      <c r="W94" t="s">
+      <c r="V94" t="s">
         <v>256</v>
       </c>
       <c r="X94" t="s">
@@ -10274,24 +10409,24 @@
       <c r="Z94" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="95" spans="1:26">
+      <c r="AA94" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="95" spans="1:27">
       <c r="A95" t="s">
         <v>106</v>
       </c>
-      <c r="E95" t="s">
-        <v>256</v>
-      </c>
       <c r="F95" t="s">
         <v>256</v>
       </c>
-      <c r="L95" t="s">
-        <v>256</v>
-      </c>
-      <c r="P95" t="s">
-        <v>256</v>
-      </c>
-      <c r="S95" t="s">
+      <c r="G95" t="s">
+        <v>256</v>
+      </c>
+      <c r="M95" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q95" t="s">
         <v>256</v>
       </c>
       <c r="T95" t="s">
@@ -10300,36 +10435,36 @@
       <c r="U95" t="s">
         <v>256</v>
       </c>
-      <c r="W95" t="s">
+      <c r="V95" t="s">
         <v>256</v>
       </c>
       <c r="X95" t="s">
         <v>256</v>
       </c>
-      <c r="Z95" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="96" spans="1:26">
+      <c r="Y95" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA95" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="96" spans="1:27">
       <c r="A96" t="s">
         <v>107</v>
       </c>
-      <c r="F96" t="s">
-        <v>256</v>
-      </c>
-      <c r="I96" t="s">
+      <c r="G96" t="s">
         <v>256</v>
       </c>
       <c r="J96" t="s">
         <v>256</v>
       </c>
-      <c r="N96" t="s">
-        <v>256</v>
-      </c>
-      <c r="P96" t="s">
-        <v>256</v>
-      </c>
-      <c r="R96" t="s">
+      <c r="K96" t="s">
+        <v>256</v>
+      </c>
+      <c r="O96" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q96" t="s">
         <v>256</v>
       </c>
       <c r="S96" t="s">
@@ -10341,7 +10476,7 @@
       <c r="U96" t="s">
         <v>256</v>
       </c>
-      <c r="W96" t="s">
+      <c r="V96" t="s">
         <v>256</v>
       </c>
       <c r="X96" t="s">
@@ -10353,56 +10488,59 @@
       <c r="Z96" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="97" spans="1:26">
+      <c r="AA96" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="97" spans="1:27">
       <c r="A97" t="s">
         <v>108</v>
       </c>
-      <c r="D97" t="s">
-        <v>256</v>
-      </c>
-      <c r="H97" t="s">
-        <v>256</v>
-      </c>
-      <c r="L97" t="s">
-        <v>256</v>
-      </c>
-      <c r="P97" t="s">
-        <v>256</v>
-      </c>
-      <c r="S97" t="s">
-        <v>256</v>
-      </c>
-      <c r="U97" t="s">
-        <v>256</v>
-      </c>
-      <c r="W97" t="s">
+      <c r="E97" t="s">
+        <v>256</v>
+      </c>
+      <c r="I97" t="s">
+        <v>256</v>
+      </c>
+      <c r="M97" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>256</v>
+      </c>
+      <c r="T97" t="s">
+        <v>256</v>
+      </c>
+      <c r="V97" t="s">
         <v>256</v>
       </c>
       <c r="X97" t="s">
         <v>256</v>
       </c>
-      <c r="Z97" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="98" spans="1:26">
+      <c r="Y97" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA97" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="98" spans="1:27">
       <c r="A98" t="s">
         <v>109</v>
       </c>
       <c r="C98" t="s">
         <v>256</v>
       </c>
-      <c r="E98" t="s">
+      <c r="D98" t="s">
         <v>256</v>
       </c>
       <c r="F98" t="s">
         <v>256</v>
       </c>
-      <c r="L98" t="s">
-        <v>256</v>
-      </c>
-      <c r="O98" t="s">
+      <c r="G98" t="s">
+        <v>256</v>
+      </c>
+      <c r="M98" t="s">
         <v>256</v>
       </c>
       <c r="P98" t="s">
@@ -10423,7 +10561,7 @@
       <c r="U98" t="s">
         <v>256</v>
       </c>
-      <c r="W98" t="s">
+      <c r="V98" t="s">
         <v>256</v>
       </c>
       <c r="X98" t="s">
@@ -10435,33 +10573,36 @@
       <c r="Z98" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="99" spans="1:26">
+      <c r="AA98" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="99" spans="1:27">
       <c r="A99" t="s">
         <v>110</v>
       </c>
       <c r="C99" t="s">
         <v>256</v>
       </c>
-      <c r="F99" t="s">
-        <v>256</v>
-      </c>
-      <c r="L99" t="s">
-        <v>256</v>
-      </c>
-      <c r="O99" t="s">
+      <c r="D99" t="s">
+        <v>256</v>
+      </c>
+      <c r="G99" t="s">
+        <v>256</v>
+      </c>
+      <c r="M99" t="s">
         <v>256</v>
       </c>
       <c r="P99" t="s">
         <v>256</v>
       </c>
-      <c r="S99" t="s">
-        <v>256</v>
-      </c>
-      <c r="U99" t="s">
-        <v>256</v>
-      </c>
-      <c r="W99" t="s">
+      <c r="Q99" t="s">
+        <v>256</v>
+      </c>
+      <c r="T99" t="s">
+        <v>256</v>
+      </c>
+      <c r="V99" t="s">
         <v>256</v>
       </c>
       <c r="X99" t="s">
@@ -10473,24 +10614,24 @@
       <c r="Z99" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="100" spans="1:26">
+      <c r="AA99" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="100" spans="1:27">
       <c r="A100" t="s">
         <v>111</v>
       </c>
       <c r="C100" t="s">
         <v>256</v>
       </c>
-      <c r="E100" t="s">
-        <v>256</v>
-      </c>
       <c r="F100" t="s">
         <v>256</v>
       </c>
-      <c r="L100" t="s">
-        <v>256</v>
-      </c>
-      <c r="P100" t="s">
+      <c r="G100" t="s">
+        <v>256</v>
+      </c>
+      <c r="M100" t="s">
         <v>256</v>
       </c>
       <c r="Q100" t="s">
@@ -10508,7 +10649,7 @@
       <c r="U100" t="s">
         <v>256</v>
       </c>
-      <c r="W100" t="s">
+      <c r="V100" t="s">
         <v>256</v>
       </c>
       <c r="X100" t="s">
@@ -10520,24 +10661,27 @@
       <c r="Z100" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="101" spans="1:26">
+      <c r="AA100" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="101" spans="1:27">
       <c r="A101" t="s">
         <v>112</v>
       </c>
       <c r="C101" t="s">
         <v>256</v>
       </c>
-      <c r="E101" t="s">
+      <c r="D101" t="s">
         <v>256</v>
       </c>
       <c r="F101" t="s">
         <v>256</v>
       </c>
-      <c r="L101" t="s">
-        <v>256</v>
-      </c>
-      <c r="N101" t="s">
+      <c r="G101" t="s">
+        <v>256</v>
+      </c>
+      <c r="M101" t="s">
         <v>256</v>
       </c>
       <c r="O101" t="s">
@@ -10549,7 +10693,7 @@
       <c r="Q101" t="s">
         <v>256</v>
       </c>
-      <c r="S101" t="s">
+      <c r="R101" t="s">
         <v>256</v>
       </c>
       <c r="T101" t="s">
@@ -10558,7 +10702,7 @@
       <c r="U101" t="s">
         <v>256</v>
       </c>
-      <c r="W101" t="s">
+      <c r="V101" t="s">
         <v>256</v>
       </c>
       <c r="X101" t="s">
@@ -10570,21 +10714,24 @@
       <c r="Z101" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="102" spans="1:26">
+      <c r="AA101" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="102" spans="1:27">
       <c r="A102" t="s">
         <v>113</v>
       </c>
-      <c r="E102" t="s">
+      <c r="D102" t="s">
         <v>256</v>
       </c>
       <c r="F102" t="s">
         <v>256</v>
       </c>
-      <c r="L102" t="s">
-        <v>256</v>
-      </c>
-      <c r="O102" t="s">
+      <c r="G102" t="s">
+        <v>256</v>
+      </c>
+      <c r="M102" t="s">
         <v>256</v>
       </c>
       <c r="P102" t="s">
@@ -10605,7 +10752,7 @@
       <c r="U102" t="s">
         <v>256</v>
       </c>
-      <c r="W102" t="s">
+      <c r="V102" t="s">
         <v>256</v>
       </c>
       <c r="X102" t="s">
@@ -10617,8 +10764,11 @@
       <c r="Z102" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="103" spans="1:26">
+      <c r="AA102" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="103" spans="1:27">
       <c r="A103" t="s">
         <v>114</v>
       </c>
@@ -10631,13 +10781,13 @@
       <c r="F103" t="s">
         <v>256</v>
       </c>
-      <c r="H103" t="s">
-        <v>256</v>
-      </c>
-      <c r="L103" t="s">
-        <v>256</v>
-      </c>
-      <c r="O103" t="s">
+      <c r="G103" t="s">
+        <v>256</v>
+      </c>
+      <c r="I103" t="s">
+        <v>256</v>
+      </c>
+      <c r="M103" t="s">
         <v>256</v>
       </c>
       <c r="P103" t="s">
@@ -10658,7 +10808,7 @@
       <c r="U103" t="s">
         <v>256</v>
       </c>
-      <c r="W103" t="s">
+      <c r="V103" t="s">
         <v>256</v>
       </c>
       <c r="X103" t="s">
@@ -10670,24 +10820,24 @@
       <c r="Z103" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="104" spans="1:26">
+      <c r="AA103" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="104" spans="1:27">
       <c r="A104" t="s">
         <v>115</v>
       </c>
       <c r="C104" t="s">
         <v>256</v>
       </c>
-      <c r="D104" t="s">
-        <v>256</v>
-      </c>
-      <c r="P104" t="s">
+      <c r="E104" t="s">
         <v>256</v>
       </c>
       <c r="Q104" t="s">
         <v>256</v>
       </c>
-      <c r="S104" t="s">
+      <c r="R104" t="s">
         <v>256</v>
       </c>
       <c r="T104" t="s">
@@ -10696,33 +10846,33 @@
       <c r="U104" t="s">
         <v>256</v>
       </c>
-      <c r="W104" t="s">
+      <c r="V104" t="s">
         <v>256</v>
       </c>
       <c r="X104" t="s">
         <v>256</v>
       </c>
-      <c r="Z104" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="105" spans="1:26">
+      <c r="Y104" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA104" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="105" spans="1:27">
       <c r="A105" t="s">
         <v>116</v>
       </c>
-      <c r="E105" t="s">
-        <v>256</v>
-      </c>
       <c r="F105" t="s">
         <v>256</v>
       </c>
-      <c r="L105" t="s">
-        <v>256</v>
-      </c>
-      <c r="P105" t="s">
-        <v>256</v>
-      </c>
-      <c r="R105" t="s">
+      <c r="G105" t="s">
+        <v>256</v>
+      </c>
+      <c r="M105" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q105" t="s">
         <v>256</v>
       </c>
       <c r="S105" t="s">
@@ -10734,65 +10884,68 @@
       <c r="U105" t="s">
         <v>256</v>
       </c>
-      <c r="W105" t="s">
+      <c r="V105" t="s">
         <v>256</v>
       </c>
       <c r="X105" t="s">
         <v>256</v>
       </c>
-      <c r="Z105" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="106" spans="1:26">
+      <c r="Y105" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA105" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="106" spans="1:27">
       <c r="A106" t="s">
         <v>117</v>
       </c>
       <c r="C106" t="s">
         <v>256</v>
       </c>
-      <c r="F106" t="s">
-        <v>256</v>
-      </c>
-      <c r="L106" t="s">
-        <v>256</v>
-      </c>
-      <c r="P106" t="s">
-        <v>256</v>
-      </c>
-      <c r="U106" t="s">
-        <v>256</v>
-      </c>
-      <c r="W106" t="s">
+      <c r="G106" t="s">
+        <v>256</v>
+      </c>
+      <c r="M106" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>256</v>
+      </c>
+      <c r="V106" t="s">
         <v>256</v>
       </c>
       <c r="X106" t="s">
         <v>256</v>
       </c>
-      <c r="Z106" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="107" spans="1:26">
+      <c r="Y106" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA106" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="107" spans="1:27">
       <c r="A107" t="s">
         <v>118</v>
       </c>
-      <c r="E107" t="s">
+      <c r="D107" t="s">
         <v>256</v>
       </c>
       <c r="F107" t="s">
         <v>256</v>
       </c>
-      <c r="L107" t="s">
-        <v>256</v>
-      </c>
-      <c r="O107" t="s">
+      <c r="G107" t="s">
+        <v>256</v>
+      </c>
+      <c r="M107" t="s">
         <v>256</v>
       </c>
       <c r="P107" t="s">
         <v>256</v>
       </c>
-      <c r="R107" t="s">
+      <c r="Q107" t="s">
         <v>256</v>
       </c>
       <c r="S107" t="s">
@@ -10804,7 +10957,7 @@
       <c r="U107" t="s">
         <v>256</v>
       </c>
-      <c r="W107" t="s">
+      <c r="V107" t="s">
         <v>256</v>
       </c>
       <c r="X107" t="s">
@@ -10816,24 +10969,24 @@
       <c r="Z107" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="108" spans="1:26">
+      <c r="AA107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="108" spans="1:27">
       <c r="A108" t="s">
         <v>119</v>
       </c>
       <c r="C108" t="s">
         <v>256</v>
       </c>
-      <c r="E108" t="s">
-        <v>256</v>
-      </c>
       <c r="F108" t="s">
         <v>256</v>
       </c>
-      <c r="L108" t="s">
-        <v>256</v>
-      </c>
-      <c r="P108" t="s">
+      <c r="G108" t="s">
+        <v>256</v>
+      </c>
+      <c r="M108" t="s">
         <v>256</v>
       </c>
       <c r="Q108" t="s">
@@ -10866,24 +11019,27 @@
       <c r="Z108" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="109" spans="1:26">
+      <c r="AA108" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="109" spans="1:27">
       <c r="A109" t="s">
         <v>120</v>
       </c>
       <c r="C109" t="s">
         <v>256</v>
       </c>
-      <c r="E109" t="s">
+      <c r="D109" t="s">
         <v>256</v>
       </c>
       <c r="F109" t="s">
         <v>256</v>
       </c>
-      <c r="L109" t="s">
-        <v>256</v>
-      </c>
-      <c r="O109" t="s">
+      <c r="G109" t="s">
+        <v>256</v>
+      </c>
+      <c r="M109" t="s">
         <v>256</v>
       </c>
       <c r="P109" t="s">
@@ -10904,7 +11060,7 @@
       <c r="U109" t="s">
         <v>256</v>
       </c>
-      <c r="W109" t="s">
+      <c r="V109" t="s">
         <v>256</v>
       </c>
       <c r="X109" t="s">
@@ -10916,21 +11072,21 @@
       <c r="Z109" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="110" spans="1:26">
+      <c r="AA109" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="110" spans="1:27">
       <c r="A110" t="s">
         <v>121</v>
       </c>
       <c r="B110" t="s">
         <v>256</v>
       </c>
-      <c r="F110" t="s">
-        <v>256</v>
-      </c>
-      <c r="L110" t="s">
-        <v>256</v>
-      </c>
-      <c r="P110" t="s">
+      <c r="G110" t="s">
+        <v>256</v>
+      </c>
+      <c r="M110" t="s">
         <v>256</v>
       </c>
       <c r="Q110" t="s">
@@ -10948,7 +11104,7 @@
       <c r="U110" t="s">
         <v>256</v>
       </c>
-      <c r="X110" t="s">
+      <c r="V110" t="s">
         <v>256</v>
       </c>
       <c r="Y110" t="s">
@@ -10957,24 +11113,27 @@
       <c r="Z110" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="111" spans="1:26">
+      <c r="AA110" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="111" spans="1:27">
       <c r="A111" t="s">
         <v>122</v>
       </c>
       <c r="C111" t="s">
         <v>256</v>
       </c>
-      <c r="E111" t="s">
+      <c r="D111" t="s">
         <v>256</v>
       </c>
       <c r="F111" t="s">
         <v>256</v>
       </c>
-      <c r="L111" t="s">
-        <v>256</v>
-      </c>
-      <c r="O111" t="s">
+      <c r="G111" t="s">
+        <v>256</v>
+      </c>
+      <c r="M111" t="s">
         <v>256</v>
       </c>
       <c r="P111" t="s">
@@ -10995,7 +11154,7 @@
       <c r="U111" t="s">
         <v>256</v>
       </c>
-      <c r="W111" t="s">
+      <c r="V111" t="s">
         <v>256</v>
       </c>
       <c r="X111" t="s">
@@ -11007,24 +11166,27 @@
       <c r="Z111" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="112" spans="1:26">
+      <c r="AA111" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="112" spans="1:27">
       <c r="A112" t="s">
         <v>123</v>
       </c>
       <c r="C112" t="s">
         <v>256</v>
       </c>
-      <c r="E112" t="s">
+      <c r="D112" t="s">
         <v>256</v>
       </c>
       <c r="F112" t="s">
         <v>256</v>
       </c>
-      <c r="L112" t="s">
-        <v>256</v>
-      </c>
-      <c r="O112" t="s">
+      <c r="G112" t="s">
+        <v>256</v>
+      </c>
+      <c r="M112" t="s">
         <v>256</v>
       </c>
       <c r="P112" t="s">
@@ -11045,7 +11207,7 @@
       <c r="U112" t="s">
         <v>256</v>
       </c>
-      <c r="W112" t="s">
+      <c r="V112" t="s">
         <v>256</v>
       </c>
       <c r="X112" t="s">
@@ -11057,18 +11219,21 @@
       <c r="Z112" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="113" spans="1:26">
+      <c r="AA112" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="113" spans="1:27">
       <c r="A113" t="s">
         <v>124</v>
       </c>
       <c r="D113" t="s">
         <v>256</v>
       </c>
-      <c r="F113" t="s">
-        <v>256</v>
-      </c>
-      <c r="H113" t="s">
+      <c r="E113" t="s">
+        <v>256</v>
+      </c>
+      <c r="G113" t="s">
         <v>256</v>
       </c>
       <c r="I113" t="s">
@@ -11077,25 +11242,25 @@
       <c r="J113" t="s">
         <v>256</v>
       </c>
-      <c r="L113" t="s">
-        <v>256</v>
-      </c>
-      <c r="O113" t="s">
+      <c r="K113" t="s">
+        <v>256</v>
+      </c>
+      <c r="M113" t="s">
         <v>256</v>
       </c>
       <c r="P113" t="s">
         <v>256</v>
       </c>
-      <c r="R113" t="s">
+      <c r="Q113" t="s">
         <v>256</v>
       </c>
       <c r="S113" t="s">
         <v>256</v>
       </c>
-      <c r="U113" t="s">
-        <v>256</v>
-      </c>
-      <c r="W113" t="s">
+      <c r="T113" t="s">
+        <v>256</v>
+      </c>
+      <c r="V113" t="s">
         <v>256</v>
       </c>
       <c r="X113" t="s">
@@ -11107,30 +11272,33 @@
       <c r="Z113" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="114" spans="1:26">
+      <c r="AA113" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="114" spans="1:27">
       <c r="A114" t="s">
         <v>125</v>
       </c>
       <c r="C114" t="s">
         <v>256</v>
       </c>
-      <c r="E114" t="s">
+      <c r="D114" t="s">
         <v>256</v>
       </c>
       <c r="F114" t="s">
         <v>256</v>
       </c>
-      <c r="L114" t="s">
-        <v>256</v>
-      </c>
-      <c r="O114" t="s">
+      <c r="G114" t="s">
+        <v>256</v>
+      </c>
+      <c r="M114" t="s">
         <v>256</v>
       </c>
       <c r="P114" t="s">
         <v>256</v>
       </c>
-      <c r="R114" t="s">
+      <c r="Q114" t="s">
         <v>256</v>
       </c>
       <c r="S114" t="s">
@@ -11142,7 +11310,7 @@
       <c r="U114" t="s">
         <v>256</v>
       </c>
-      <c r="W114" t="s">
+      <c r="V114" t="s">
         <v>256</v>
       </c>
       <c r="X114" t="s">
@@ -11152,6 +11320,9 @@
         <v>256</v>
       </c>
       <c r="Z114" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA114" t="s">
         <v>256</v>
       </c>
     </row>
@@ -11170,79 +11341,79 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="R1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="T1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="V1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="W1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="X1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Y1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Z1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:26">
@@ -16079,10 +16250,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="B1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:3">
